--- a/translators/translator_template.xlsx
+++ b/translators/translator_template.xlsx
@@ -16079,7 +16079,7 @@
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (A1-A3)</t>
+          <t>Photochemical Ozone Creation Potential (A1-A3)</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (A4)</t>
+          <t>Photochemical Ozone Creation Potential (A4)</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (A5)</t>
+          <t>Photochemical Ozone Creation Potential (A5)</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B1)</t>
+          <t>Photochemical Ozone Creation Potential (B1)</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B2)</t>
+          <t>Photochemical Ozone Creation Potential (B2)</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B3)</t>
+          <t>Photochemical Ozone Creation Potential (B3)</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B4)</t>
+          <t>Photochemical Ozone Creation Potential (B4)</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B5)</t>
+          <t>Photochemical Ozone Creation Potential (B5)</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B6)</t>
+          <t>Photochemical Ozone Creation Potential (B6)</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (C1)</t>
+          <t>Photochemical Ozone Creation Potential (C1)</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (C2)</t>
+          <t>Photochemical Ozone Creation Potential (C2)</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (C3)</t>
+          <t>Photochemical Ozone Creation Potential (C3)</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (C4)</t>
+          <t>Photochemical Ozone Creation Potential (C4)</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -16378,7 +16378,7 @@
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (D)</t>
+          <t>Photochemical Ozone Creation Potential (D)</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (D1)</t>
+          <t>Photochemical Ozone Creation Potential (D1)</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (D2)</t>
+          <t>Photochemical Ozone Creation Potential (D2)</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>Total Photochemical Ozone Formation Potential</t>
+          <t>Total Photochemical Ozone Creation Potential</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential</t>
+          <t>Photochemical Ozone Creation Potential</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">

--- a/translators/translator_template.xlsx
+++ b/translators/translator_template.xlsx
@@ -4020,9 +4020,9 @@
           <t>date</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>

--- a/translators/translator_template.xlsx
+++ b/translators/translator_template.xlsx
@@ -2949,7 +2949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2958,6 +2958,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2991,6 +2992,11 @@
           <t>Default value</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Preprocess rule</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
@@ -3014,6 +3020,7 @@
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -3037,6 +3044,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -3060,6 +3068,7 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -3083,6 +3092,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -3106,6 +3116,7 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -3129,6 +3140,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -3152,6 +3164,7 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -3175,6 +3188,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -3198,6 +3212,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -3221,6 +3236,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -3244,6 +3260,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -3267,6 +3284,7 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -3290,6 +3308,7 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -3313,6 +3332,7 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -3336,6 +3356,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -3359,6 +3380,7 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -3382,6 +3404,7 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -3405,6 +3428,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -3428,6 +3452,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -3451,6 +3476,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -3474,6 +3500,7 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -3497,6 +3524,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
@@ -3520,6 +3548,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
@@ -3543,6 +3572,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
@@ -3566,6 +3596,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
@@ -3589,6 +3620,7 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
@@ -3612,6 +3644,7 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
@@ -3635,6 +3668,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
@@ -3658,6 +3692,7 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
@@ -3681,6 +3716,7 @@
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
@@ -3704,6 +3740,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
@@ -3727,6 +3764,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
@@ -3750,6 +3788,7 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
@@ -3773,6 +3812,7 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="2" t="inlineStr">
@@ -3796,6 +3836,7 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="2" t="inlineStr">
@@ -3819,6 +3860,7 @@
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="2" t="inlineStr">
@@ -3842,6 +3884,7 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="2" t="inlineStr">
@@ -3865,6 +3908,7 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="2" t="inlineStr">
@@ -3888,6 +3932,7 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="2" t="inlineStr">
@@ -3911,6 +3956,7 @@
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="2" t="inlineStr">
@@ -3934,6 +3980,7 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="2" t="inlineStr">
@@ -3957,6 +4004,7 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="2" t="inlineStr">
@@ -3980,6 +4028,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="2" t="inlineStr">
@@ -4003,6 +4052,7 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="2" t="inlineStr">
@@ -4026,6 +4076,7 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="2" t="inlineStr">
@@ -4049,6 +4100,7 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="2" t="inlineStr">
@@ -4072,6 +4124,7 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="2" t="inlineStr">
@@ -4095,6 +4148,7 @@
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="2" t="inlineStr">
@@ -4118,6 +4172,7 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="2" t="inlineStr">
@@ -4141,6 +4196,7 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="2" t="inlineStr">
@@ -4164,6 +4220,7 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="2" t="inlineStr">
@@ -4187,6 +4244,7 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="2" t="inlineStr">
@@ -4210,6 +4268,7 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="2" t="inlineStr">
@@ -4233,6 +4292,7 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="2" t="inlineStr">
@@ -4256,6 +4316,7 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="2" t="inlineStr">
@@ -4279,6 +4340,7 @@
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="2" t="inlineStr">
@@ -4302,6 +4364,7 @@
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="2" t="inlineStr">
@@ -4325,6 +4388,7 @@
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="2" t="inlineStr">
@@ -4348,6 +4412,7 @@
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="2" t="inlineStr">
@@ -4371,6 +4436,7 @@
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="2" t="inlineStr">
@@ -4394,6 +4460,7 @@
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="2" t="inlineStr">
@@ -4417,6 +4484,7 @@
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="2" t="inlineStr">
@@ -4440,6 +4508,7 @@
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="2" t="inlineStr">
@@ -4463,6 +4532,7 @@
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="2" t="inlineStr">
@@ -4486,6 +4556,7 @@
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="2" t="inlineStr">
@@ -4509,6 +4580,7 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="2" t="inlineStr">
@@ -4532,6 +4604,7 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="2" t="inlineStr">
@@ -4555,6 +4628,7 @@
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="2" t="inlineStr">
@@ -4578,6 +4652,7 @@
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="2" t="inlineStr">
@@ -4601,6 +4676,7 @@
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="2" t="inlineStr">
@@ -4624,6 +4700,7 @@
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="2" t="inlineStr">
@@ -4647,6 +4724,7 @@
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="2" t="inlineStr">
@@ -4670,6 +4748,7 @@
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="2" t="inlineStr">
@@ -4693,6 +4772,7 @@
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="2" t="inlineStr">
@@ -4716,6 +4796,7 @@
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="2" t="inlineStr">
@@ -4739,6 +4820,7 @@
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="2" t="inlineStr">
@@ -4762,6 +4844,7 @@
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="2" t="inlineStr">
@@ -4785,6 +4868,7 @@
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="2" t="inlineStr">
@@ -4808,6 +4892,7 @@
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="2" t="inlineStr">
@@ -4831,6 +4916,7 @@
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="2" t="inlineStr">
@@ -4854,6 +4940,7 @@
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="2" t="inlineStr">
@@ -4877,6 +4964,7 @@
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="2" t="inlineStr">
@@ -4900,6 +4988,7 @@
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="2" t="inlineStr">
@@ -4923,6 +5012,7 @@
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="2" t="inlineStr">
@@ -4946,6 +5036,7 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="2" t="inlineStr">
@@ -4969,6 +5060,7 @@
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="2" t="inlineStr">
@@ -4992,6 +5084,7 @@
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="2" t="inlineStr">
@@ -5015,6 +5108,7 @@
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="2" t="inlineStr">
@@ -5038,6 +5132,7 @@
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="2" t="inlineStr">
@@ -5061,6 +5156,7 @@
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="2" t="inlineStr">
@@ -5084,6 +5180,7 @@
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="2" t="inlineStr">
@@ -5107,6 +5204,7 @@
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="2" t="inlineStr">
@@ -5130,6 +5228,7 @@
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="2" t="inlineStr">
@@ -5153,6 +5252,7 @@
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="2" t="inlineStr">
@@ -5176,6 +5276,7 @@
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="2" t="inlineStr">
@@ -5199,6 +5300,7 @@
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="2" t="inlineStr">
@@ -5222,6 +5324,7 @@
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="2" t="inlineStr">
@@ -5245,6 +5348,7 @@
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="2" t="inlineStr">
@@ -5268,6 +5372,7 @@
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="2" t="inlineStr">
@@ -5291,6 +5396,7 @@
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="2" t="inlineStr">
@@ -5314,6 +5420,7 @@
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="2" t="inlineStr">
@@ -5337,6 +5444,7 @@
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="2" t="inlineStr">
@@ -5360,6 +5468,7 @@
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="2" t="inlineStr">
@@ -5383,6 +5492,7 @@
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="2" t="inlineStr">
@@ -5406,6 +5516,7 @@
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="2" t="inlineStr">
@@ -5429,6 +5540,7 @@
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="2" t="inlineStr">
@@ -5452,6 +5564,7 @@
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="2" t="inlineStr">
@@ -5475,6 +5588,7 @@
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="2" t="inlineStr">
@@ -5498,6 +5612,7 @@
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="2" t="inlineStr">
@@ -5521,6 +5636,7 @@
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="B112" s="2" t="inlineStr">
@@ -5544,6 +5660,7 @@
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="B113" s="2" t="inlineStr">
@@ -5567,6 +5684,7 @@
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="B114" s="2" t="inlineStr">
@@ -5590,6 +5708,7 @@
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="B115" s="2" t="inlineStr">
@@ -5613,6 +5732,7 @@
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="B116" s="2" t="inlineStr">
@@ -5636,6 +5756,7 @@
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="B117" s="2" t="inlineStr">
@@ -5659,6 +5780,7 @@
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="B118" s="2" t="inlineStr">
@@ -5682,6 +5804,7 @@
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="B119" s="2" t="inlineStr">
@@ -5705,6 +5828,7 @@
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="B120" s="2" t="inlineStr">
@@ -5728,6 +5852,7 @@
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="B121" s="2" t="inlineStr">
@@ -5751,6 +5876,7 @@
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="B122" s="2" t="inlineStr">
@@ -5774,6 +5900,7 @@
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="B123" s="2" t="inlineStr">
@@ -5797,6 +5924,7 @@
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="B124" s="2" t="inlineStr">
@@ -5820,6 +5948,7 @@
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="B125" s="2" t="inlineStr">
@@ -5843,6 +5972,7 @@
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="B126" s="2" t="inlineStr">
@@ -5866,6 +5996,7 @@
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="B127" s="2" t="inlineStr">
@@ -5889,6 +6020,7 @@
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="B128" s="2" t="inlineStr">
@@ -5912,6 +6044,7 @@
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="B129" s="2" t="inlineStr">
@@ -5935,6 +6068,7 @@
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="B130" s="2" t="inlineStr">
@@ -5958,6 +6092,7 @@
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="B131" s="2" t="inlineStr">
@@ -5981,6 +6116,7 @@
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="B132" s="2" t="inlineStr">
@@ -6004,6 +6140,7 @@
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="B133" s="2" t="inlineStr">
@@ -6027,6 +6164,7 @@
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="B134" s="2" t="inlineStr">
@@ -6050,6 +6188,7 @@
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="B135" s="2" t="inlineStr">
@@ -6073,6 +6212,7 @@
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="B136" s="2" t="inlineStr">
@@ -6096,6 +6236,7 @@
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr"/>
+      <c r="G136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="B137" s="2" t="inlineStr">
@@ -6119,6 +6260,7 @@
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr"/>
+      <c r="G137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="B138" s="2" t="inlineStr">
@@ -6142,6 +6284,7 @@
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="B139" s="2" t="inlineStr">
@@ -6165,6 +6308,7 @@
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr"/>
+      <c r="G139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="B140" s="2" t="inlineStr">
@@ -6188,6 +6332,7 @@
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="B141" s="2" t="inlineStr">
@@ -6211,6 +6356,7 @@
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11291,7 +11437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11300,6 +11446,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11333,6 +11480,11 @@
           <t>Default value</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Preprocess rule</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
@@ -11356,6 +11508,7 @@
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -11379,6 +11532,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -11402,6 +11556,7 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -11425,6 +11580,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -11448,6 +11604,7 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -11471,6 +11628,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -11494,6 +11652,7 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -11517,6 +11676,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -11540,6 +11700,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -11563,6 +11724,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -11586,6 +11748,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -11609,6 +11772,7 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -11632,6 +11796,7 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -11655,6 +11820,7 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -11678,6 +11844,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -11701,6 +11868,7 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -11724,6 +11892,7 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -11747,6 +11916,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12095,7 +12265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F342"/>
+  <dimension ref="A1:G342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -12104,6 +12274,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12137,6 +12308,11 @@
           <t>Default value</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Preprocess rule</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
@@ -12160,6 +12336,7 @@
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -12183,6 +12360,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -12206,6 +12384,7 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -12229,6 +12408,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -12252,6 +12432,7 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -12275,6 +12456,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -12298,6 +12480,7 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -12321,6 +12504,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -12344,6 +12528,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -12367,6 +12552,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -12390,6 +12576,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -12413,6 +12600,7 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -12436,6 +12624,7 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -12459,6 +12648,7 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -12482,6 +12672,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -12505,6 +12696,7 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -12528,6 +12720,7 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -12551,6 +12744,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -12574,6 +12768,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -12597,6 +12792,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -12620,6 +12816,7 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -12643,6 +12840,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
@@ -12666,6 +12864,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
@@ -12689,6 +12888,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
@@ -12712,6 +12912,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
@@ -12735,6 +12936,7 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
@@ -12758,6 +12960,7 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
@@ -12781,6 +12984,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
@@ -12804,6 +13008,7 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
@@ -12827,6 +13032,7 @@
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
@@ -12850,6 +13056,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
@@ -12873,6 +13080,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
@@ -12896,6 +13104,7 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
@@ -12919,6 +13128,7 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="2" t="inlineStr">
@@ -12942,6 +13152,7 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="2" t="inlineStr">
@@ -12965,6 +13176,7 @@
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="2" t="inlineStr">
@@ -12988,6 +13200,7 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="2" t="inlineStr">
@@ -13011,6 +13224,7 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="2" t="inlineStr">
@@ -13034,6 +13248,7 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="2" t="inlineStr">
@@ -13057,6 +13272,7 @@
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="B42" s="2" t="inlineStr">
@@ -13080,6 +13296,7 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="2" t="inlineStr">
@@ -13103,6 +13320,7 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="2" t="inlineStr">
@@ -13126,6 +13344,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="2" t="inlineStr">
@@ -13149,6 +13368,7 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="2" t="inlineStr">
@@ -13172,6 +13392,7 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="2" t="inlineStr">
@@ -13195,6 +13416,7 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="2" t="inlineStr">
@@ -13218,6 +13440,7 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="2" t="inlineStr">
@@ -13241,6 +13464,7 @@
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="2" t="inlineStr">
@@ -13264,6 +13488,7 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="B51" s="2" t="inlineStr">
@@ -13287,6 +13512,7 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" s="2" t="inlineStr">
@@ -13310,6 +13536,7 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" s="2" t="inlineStr">
@@ -13333,6 +13560,7 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="B54" s="2" t="inlineStr">
@@ -13356,6 +13584,7 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="B55" s="2" t="inlineStr">
@@ -13379,6 +13608,7 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="B56" s="2" t="inlineStr">
@@ -13402,6 +13632,7 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" s="2" t="inlineStr">
@@ -13425,6 +13656,7 @@
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="B58" s="2" t="inlineStr">
@@ -13448,6 +13680,7 @@
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="B59" s="2" t="inlineStr">
@@ -13471,6 +13704,7 @@
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" s="2" t="inlineStr">
@@ -13494,6 +13728,7 @@
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="B61" s="2" t="inlineStr">
@@ -13517,6 +13752,7 @@
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="B62" s="2" t="inlineStr">
@@ -13540,6 +13776,7 @@
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="B63" s="2" t="inlineStr">
@@ -13563,6 +13800,7 @@
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="2" t="inlineStr">
@@ -13586,6 +13824,7 @@
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="B65" s="2" t="inlineStr">
@@ -13609,6 +13848,7 @@
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="B66" s="2" t="inlineStr">
@@ -13632,6 +13872,7 @@
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="B67" s="2" t="inlineStr">
@@ -13655,6 +13896,7 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="B68" s="2" t="inlineStr">
@@ -13678,6 +13920,7 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="B69" s="2" t="inlineStr">
@@ -13701,6 +13944,7 @@
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="2" t="inlineStr">
@@ -13724,6 +13968,7 @@
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="B71" s="2" t="inlineStr">
@@ -13747,6 +13992,7 @@
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="B72" s="2" t="inlineStr">
@@ -13770,6 +14016,7 @@
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="B73" s="2" t="inlineStr">
@@ -13793,6 +14040,7 @@
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="B74" s="2" t="inlineStr">
@@ -13816,6 +14064,7 @@
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="B75" s="2" t="inlineStr">
@@ -13839,6 +14088,7 @@
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="B76" s="2" t="inlineStr">
@@ -13862,6 +14112,7 @@
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="2" t="inlineStr">
@@ -13885,6 +14136,7 @@
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="B78" s="2" t="inlineStr">
@@ -13908,6 +14160,7 @@
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="2" t="inlineStr">
@@ -13931,6 +14184,7 @@
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="2" t="inlineStr">
@@ -13954,6 +14208,7 @@
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="B81" s="2" t="inlineStr">
@@ -13977,6 +14232,7 @@
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="2" t="inlineStr">
@@ -14000,6 +14256,7 @@
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="2" t="inlineStr">
@@ -14023,6 +14280,7 @@
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="2" t="inlineStr">
@@ -14046,6 +14304,7 @@
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="2" t="inlineStr">
@@ -14069,6 +14328,7 @@
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="2" t="inlineStr">
@@ -14092,6 +14352,7 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="2" t="inlineStr">
@@ -14115,6 +14376,7 @@
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="2" t="inlineStr">
@@ -14138,6 +14400,7 @@
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="B89" s="2" t="inlineStr">
@@ -14161,6 +14424,7 @@
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="B90" s="2" t="inlineStr">
@@ -14184,6 +14448,7 @@
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="2" t="inlineStr">
@@ -14207,6 +14472,7 @@
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="B92" s="2" t="inlineStr">
@@ -14230,6 +14496,7 @@
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="B93" s="2" t="inlineStr">
@@ -14253,6 +14520,7 @@
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="B94" s="2" t="inlineStr">
@@ -14276,6 +14544,7 @@
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="B95" s="2" t="inlineStr">
@@ -14299,6 +14568,7 @@
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="2" t="inlineStr">
@@ -14322,6 +14592,7 @@
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="B97" s="2" t="inlineStr">
@@ -14345,6 +14616,7 @@
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="B98" s="2" t="inlineStr">
@@ -14368,6 +14640,7 @@
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="2" t="inlineStr">
@@ -14391,6 +14664,7 @@
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="2" t="inlineStr">
@@ -14414,6 +14688,7 @@
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="B101" s="2" t="inlineStr">
@@ -14437,6 +14712,7 @@
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="2" t="inlineStr">
@@ -14460,6 +14736,7 @@
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="B103" s="2" t="inlineStr">
@@ -14483,6 +14760,7 @@
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="B104" s="2" t="inlineStr">
@@ -14506,6 +14784,7 @@
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="B105" s="2" t="inlineStr">
@@ -14529,6 +14808,7 @@
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="B106" s="2" t="inlineStr">
@@ -14552,6 +14832,7 @@
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="B107" s="2" t="inlineStr">
@@ -14575,6 +14856,7 @@
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="B108" s="2" t="inlineStr">
@@ -14598,6 +14880,7 @@
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="B109" s="2" t="inlineStr">
@@ -14621,6 +14904,7 @@
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="B110" s="2" t="inlineStr">
@@ -14644,6 +14928,7 @@
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="B111" s="2" t="inlineStr">
@@ -14667,6 +14952,7 @@
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="B112" s="2" t="inlineStr">
@@ -14690,6 +14976,7 @@
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="B113" s="2" t="inlineStr">
@@ -14713,6 +15000,7 @@
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="B114" s="2" t="inlineStr">
@@ -14736,6 +15024,7 @@
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="B115" s="2" t="inlineStr">
@@ -14759,6 +15048,7 @@
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="B116" s="2" t="inlineStr">
@@ -14782,6 +15072,7 @@
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="B117" s="2" t="inlineStr">
@@ -14805,6 +15096,7 @@
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="B118" s="2" t="inlineStr">
@@ -14828,6 +15120,7 @@
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="B119" s="2" t="inlineStr">
@@ -14851,6 +15144,7 @@
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="B120" s="2" t="inlineStr">
@@ -14874,6 +15168,7 @@
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="B121" s="2" t="inlineStr">
@@ -14897,6 +15192,7 @@
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="B122" s="2" t="inlineStr">
@@ -14920,6 +15216,7 @@
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="B123" s="2" t="inlineStr">
@@ -14943,6 +15240,7 @@
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="B124" s="2" t="inlineStr">
@@ -14966,6 +15264,7 @@
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="B125" s="2" t="inlineStr">
@@ -14989,6 +15288,7 @@
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="B126" s="2" t="inlineStr">
@@ -15012,6 +15312,7 @@
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="B127" s="2" t="inlineStr">
@@ -15035,6 +15336,7 @@
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="B128" s="2" t="inlineStr">
@@ -15058,6 +15360,7 @@
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="B129" s="2" t="inlineStr">
@@ -15081,6 +15384,7 @@
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="B130" s="2" t="inlineStr">
@@ -15104,6 +15408,7 @@
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="B131" s="2" t="inlineStr">
@@ -15127,6 +15432,7 @@
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="B132" s="2" t="inlineStr">
@@ -15150,6 +15456,7 @@
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="B133" s="2" t="inlineStr">
@@ -15173,6 +15480,7 @@
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="B134" s="2" t="inlineStr">
@@ -15196,6 +15504,7 @@
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="B135" s="2" t="inlineStr">
@@ -15219,6 +15528,7 @@
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="B136" s="2" t="inlineStr">
@@ -15242,6 +15552,7 @@
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr"/>
+      <c r="G136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="B137" s="2" t="inlineStr">
@@ -15265,6 +15576,7 @@
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr"/>
+      <c r="G137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="B138" s="2" t="inlineStr">
@@ -15288,6 +15600,7 @@
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="B139" s="2" t="inlineStr">
@@ -15311,6 +15624,7 @@
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr"/>
+      <c r="G139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="B140" s="2" t="inlineStr">
@@ -15334,6 +15648,7 @@
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="B141" s="2" t="inlineStr">
@@ -15357,6 +15672,7 @@
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="B142" s="2" t="inlineStr">
@@ -15380,6 +15696,7 @@
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr"/>
+      <c r="G142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="B143" s="2" t="inlineStr">
@@ -15403,6 +15720,7 @@
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr"/>
+      <c r="G143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="B144" s="2" t="inlineStr">
@@ -15426,6 +15744,7 @@
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr"/>
+      <c r="G144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="B145" s="2" t="inlineStr">
@@ -15449,6 +15768,7 @@
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr"/>
+      <c r="G145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="B146" s="2" t="inlineStr">
@@ -15472,6 +15792,7 @@
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr"/>
+      <c r="G146" s="5" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="B147" s="2" t="inlineStr">
@@ -15495,6 +15816,7 @@
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr"/>
+      <c r="G147" s="5" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="B148" s="2" t="inlineStr">
@@ -15518,6 +15840,7 @@
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr"/>
+      <c r="G148" s="5" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="B149" s="2" t="inlineStr">
@@ -15541,6 +15864,7 @@
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr"/>
+      <c r="G149" s="5" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="B150" s="2" t="inlineStr">
@@ -15564,6 +15888,7 @@
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr"/>
+      <c r="G150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="B151" s="2" t="inlineStr">
@@ -15587,6 +15912,7 @@
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr"/>
+      <c r="G151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="B152" s="2" t="inlineStr">
@@ -15610,6 +15936,7 @@
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr"/>
+      <c r="G152" s="5" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="B153" s="2" t="inlineStr">
@@ -15633,6 +15960,7 @@
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr"/>
+      <c r="G153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="B154" s="2" t="inlineStr">
@@ -15656,6 +15984,7 @@
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr"/>
+      <c r="G154" s="5" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="B155" s="2" t="inlineStr">
@@ -15679,6 +16008,7 @@
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr"/>
+      <c r="G155" s="5" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="B156" s="2" t="inlineStr">
@@ -15702,6 +16032,7 @@
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr"/>
+      <c r="G156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="B157" s="2" t="inlineStr">
@@ -15725,6 +16056,7 @@
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr"/>
+      <c r="G157" s="5" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="B158" s="2" t="inlineStr">
@@ -15748,6 +16080,7 @@
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr"/>
+      <c r="G158" s="5" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="B159" s="2" t="inlineStr">
@@ -15771,6 +16104,7 @@
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr"/>
+      <c r="G159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="B160" s="2" t="inlineStr">
@@ -15794,6 +16128,7 @@
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr"/>
+      <c r="G160" s="5" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="B161" s="2" t="inlineStr">
@@ -15817,6 +16152,7 @@
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr"/>
+      <c r="G161" s="5" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="B162" s="2" t="inlineStr">
@@ -15840,6 +16176,7 @@
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr"/>
+      <c r="G162" s="5" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="B163" s="2" t="inlineStr">
@@ -15863,6 +16200,7 @@
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr"/>
+      <c r="G163" s="5" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="B164" s="2" t="inlineStr">
@@ -15886,6 +16224,7 @@
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr"/>
+      <c r="G164" s="5" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="B165" s="2" t="inlineStr">
@@ -15909,6 +16248,7 @@
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr"/>
+      <c r="G165" s="5" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="B166" s="2" t="inlineStr">
@@ -15932,6 +16272,7 @@
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr"/>
+      <c r="G166" s="5" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="B167" s="2" t="inlineStr">
@@ -15955,6 +16296,7 @@
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr"/>
+      <c r="G167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="B168" s="2" t="inlineStr">
@@ -15978,6 +16320,7 @@
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr"/>
+      <c r="G168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="B169" s="2" t="inlineStr">
@@ -16001,6 +16344,7 @@
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr"/>
+      <c r="G169" s="5" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="B170" s="2" t="inlineStr">
@@ -16024,6 +16368,7 @@
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr"/>
+      <c r="G170" s="5" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="B171" s="2" t="inlineStr">
@@ -16047,6 +16392,7 @@
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr"/>
+      <c r="G171" s="5" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="B172" s="2" t="inlineStr">
@@ -16070,6 +16416,7 @@
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr"/>
+      <c r="G172" s="5" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="B173" s="2" t="inlineStr">
@@ -16093,6 +16440,7 @@
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr"/>
+      <c r="G173" s="5" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="B174" s="2" t="inlineStr">
@@ -16116,6 +16464,7 @@
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr"/>
+      <c r="G174" s="5" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="B175" s="2" t="inlineStr">
@@ -16139,6 +16488,7 @@
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr"/>
+      <c r="G175" s="5" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="B176" s="2" t="inlineStr">
@@ -16162,6 +16512,7 @@
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr"/>
+      <c r="G176" s="5" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="B177" s="2" t="inlineStr">
@@ -16185,6 +16536,7 @@
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr"/>
+      <c r="G177" s="5" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="B178" s="2" t="inlineStr">
@@ -16208,6 +16560,7 @@
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr"/>
+      <c r="G178" s="5" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="B179" s="2" t="inlineStr">
@@ -16231,6 +16584,7 @@
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr"/>
+      <c r="G179" s="5" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="B180" s="2" t="inlineStr">
@@ -16254,6 +16608,7 @@
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr"/>
+      <c r="G180" s="5" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="B181" s="2" t="inlineStr">
@@ -16277,6 +16632,7 @@
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr"/>
+      <c r="G181" s="5" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="B182" s="2" t="inlineStr">
@@ -16300,6 +16656,7 @@
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr"/>
+      <c r="G182" s="5" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="B183" s="2" t="inlineStr">
@@ -16323,6 +16680,7 @@
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr"/>
+      <c r="G183" s="5" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="B184" s="2" t="inlineStr">
@@ -16346,6 +16704,7 @@
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr"/>
+      <c r="G184" s="5" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="B185" s="2" t="inlineStr">
@@ -16369,6 +16728,7 @@
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr"/>
+      <c r="G185" s="5" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="B186" s="2" t="inlineStr">
@@ -16392,6 +16752,7 @@
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr"/>
+      <c r="G186" s="5" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="B187" s="2" t="inlineStr">
@@ -16415,6 +16776,7 @@
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr"/>
+      <c r="G187" s="5" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="B188" s="2" t="inlineStr">
@@ -16438,6 +16800,7 @@
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr"/>
+      <c r="G188" s="5" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="B189" s="2" t="inlineStr">
@@ -16461,6 +16824,7 @@
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr"/>
+      <c r="G189" s="5" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="B190" s="2" t="inlineStr">
@@ -16484,6 +16848,7 @@
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr"/>
+      <c r="G190" s="5" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="B191" s="2" t="inlineStr">
@@ -16507,6 +16872,7 @@
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr"/>
+      <c r="G191" s="5" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="B192" s="2" t="inlineStr">
@@ -16530,6 +16896,7 @@
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr"/>
+      <c r="G192" s="5" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="B193" s="2" t="inlineStr">
@@ -16553,6 +16920,7 @@
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr"/>
+      <c r="G193" s="5" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="B194" s="2" t="inlineStr">
@@ -16576,6 +16944,7 @@
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr"/>
+      <c r="G194" s="5" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="B195" s="2" t="inlineStr">
@@ -16599,6 +16968,7 @@
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr"/>
+      <c r="G195" s="5" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="B196" s="2" t="inlineStr">
@@ -16622,6 +16992,7 @@
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr"/>
+      <c r="G196" s="5" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="B197" s="2" t="inlineStr">
@@ -16645,6 +17016,7 @@
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr"/>
+      <c r="G197" s="5" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="B198" s="2" t="inlineStr">
@@ -16668,6 +17040,7 @@
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr"/>
+      <c r="G198" s="5" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="B199" s="2" t="inlineStr">
@@ -16691,6 +17064,7 @@
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr"/>
+      <c r="G199" s="5" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="B200" s="2" t="inlineStr">
@@ -16714,6 +17088,7 @@
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr"/>
+      <c r="G200" s="5" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="B201" s="2" t="inlineStr">
@@ -16737,6 +17112,7 @@
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr"/>
+      <c r="G201" s="5" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="B202" s="2" t="inlineStr">
@@ -16760,6 +17136,7 @@
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr"/>
+      <c r="G202" s="5" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="B203" s="2" t="inlineStr">
@@ -16783,6 +17160,7 @@
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr"/>
+      <c r="G203" s="5" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="B204" s="2" t="inlineStr">
@@ -16806,6 +17184,7 @@
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr"/>
+      <c r="G204" s="5" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="B205" s="2" t="inlineStr">
@@ -16829,6 +17208,7 @@
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr"/>
+      <c r="G205" s="5" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="B206" s="2" t="inlineStr">
@@ -16852,6 +17232,7 @@
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr"/>
+      <c r="G206" s="5" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="B207" s="2" t="inlineStr">
@@ -16875,6 +17256,7 @@
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr"/>
+      <c r="G207" s="5" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="B208" s="2" t="inlineStr">
@@ -16898,6 +17280,7 @@
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr"/>
+      <c r="G208" s="5" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="B209" s="2" t="inlineStr">
@@ -16921,6 +17304,7 @@
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr"/>
+      <c r="G209" s="5" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="B210" s="2" t="inlineStr">
@@ -16944,6 +17328,7 @@
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr"/>
+      <c r="G210" s="5" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="B211" s="2" t="inlineStr">
@@ -16967,6 +17352,7 @@
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr"/>
+      <c r="G211" s="5" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="B212" s="2" t="inlineStr">
@@ -16990,6 +17376,7 @@
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr"/>
+      <c r="G212" s="5" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="B213" s="2" t="inlineStr">
@@ -17013,6 +17400,7 @@
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr"/>
+      <c r="G213" s="5" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="B214" s="2" t="inlineStr">
@@ -17036,6 +17424,7 @@
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr"/>
+      <c r="G214" s="5" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="B215" s="2" t="inlineStr">
@@ -17059,6 +17448,7 @@
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr"/>
+      <c r="G215" s="5" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="B216" s="2" t="inlineStr">
@@ -17082,6 +17472,7 @@
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr"/>
+      <c r="G216" s="5" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="B217" s="2" t="inlineStr">
@@ -17105,6 +17496,7 @@
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr"/>
+      <c r="G217" s="5" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="B218" s="2" t="inlineStr">
@@ -17128,6 +17520,7 @@
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr"/>
+      <c r="G218" s="5" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="B219" s="2" t="inlineStr">
@@ -17151,6 +17544,7 @@
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr"/>
+      <c r="G219" s="5" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="B220" s="2" t="inlineStr">
@@ -17174,6 +17568,7 @@
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr"/>
+      <c r="G220" s="5" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="B221" s="2" t="inlineStr">
@@ -17197,6 +17592,7 @@
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr"/>
+      <c r="G221" s="5" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="B222" s="2" t="inlineStr">
@@ -17220,6 +17616,7 @@
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr"/>
+      <c r="G222" s="5" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="B223" s="2" t="inlineStr">
@@ -17243,6 +17640,7 @@
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr"/>
+      <c r="G223" s="5" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="B224" s="2" t="inlineStr">
@@ -17266,6 +17664,7 @@
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr"/>
+      <c r="G224" s="5" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="B225" s="2" t="inlineStr">
@@ -17289,6 +17688,7 @@
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr"/>
+      <c r="G225" s="5" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="B226" s="2" t="inlineStr">
@@ -17312,6 +17712,7 @@
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr"/>
+      <c r="G226" s="5" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="B227" s="2" t="inlineStr">
@@ -17335,6 +17736,7 @@
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr"/>
+      <c r="G227" s="5" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="B228" s="2" t="inlineStr">
@@ -17358,6 +17760,7 @@
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr"/>
+      <c r="G228" s="5" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="B229" s="2" t="inlineStr">
@@ -17381,6 +17784,7 @@
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr"/>
+      <c r="G229" s="5" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="B230" s="2" t="inlineStr">
@@ -17404,6 +17808,7 @@
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr"/>
+      <c r="G230" s="5" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="B231" s="2" t="inlineStr">
@@ -17427,6 +17832,7 @@
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr"/>
+      <c r="G231" s="5" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="B232" s="2" t="inlineStr">
@@ -17450,6 +17856,7 @@
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr"/>
+      <c r="G232" s="5" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="B233" s="2" t="inlineStr">
@@ -17473,6 +17880,7 @@
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr"/>
+      <c r="G233" s="5" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="B234" s="2" t="inlineStr">
@@ -17496,6 +17904,7 @@
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr"/>
+      <c r="G234" s="5" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="B235" s="2" t="inlineStr">
@@ -17519,6 +17928,7 @@
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr"/>
+      <c r="G235" s="5" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="B236" s="2" t="inlineStr">
@@ -17542,6 +17952,7 @@
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr"/>
+      <c r="G236" s="5" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="B237" s="2" t="inlineStr">
@@ -17565,6 +17976,7 @@
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr"/>
+      <c r="G237" s="5" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="B238" s="2" t="inlineStr">
@@ -17588,6 +18000,7 @@
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr"/>
+      <c r="G238" s="5" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="B239" s="2" t="inlineStr">
@@ -17611,6 +18024,7 @@
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr"/>
+      <c r="G239" s="5" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="B240" s="2" t="inlineStr">
@@ -17634,6 +18048,7 @@
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr"/>
+      <c r="G240" s="5" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="B241" s="2" t="inlineStr">
@@ -17657,6 +18072,7 @@
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr"/>
+      <c r="G241" s="5" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="B242" s="2" t="inlineStr">
@@ -17680,6 +18096,7 @@
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr"/>
+      <c r="G242" s="5" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="B243" s="2" t="inlineStr">
@@ -17703,6 +18120,7 @@
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr"/>
+      <c r="G243" s="5" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="B244" s="2" t="inlineStr">
@@ -17726,6 +18144,7 @@
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr"/>
+      <c r="G244" s="5" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="B245" s="2" t="inlineStr">
@@ -17749,6 +18168,7 @@
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr"/>
+      <c r="G245" s="5" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="B246" s="2" t="inlineStr">
@@ -17772,6 +18192,7 @@
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr"/>
+      <c r="G246" s="5" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="B247" s="2" t="inlineStr">
@@ -17795,6 +18216,7 @@
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr"/>
+      <c r="G247" s="5" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="B248" s="2" t="inlineStr">
@@ -17818,6 +18240,7 @@
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr"/>
+      <c r="G248" s="5" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="B249" s="2" t="inlineStr">
@@ -17841,6 +18264,7 @@
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr"/>
+      <c r="G249" s="5" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="B250" s="2" t="inlineStr">
@@ -17864,6 +18288,7 @@
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr"/>
+      <c r="G250" s="5" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="B251" s="2" t="inlineStr">
@@ -17887,6 +18312,7 @@
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr"/>
+      <c r="G251" s="5" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="B252" s="2" t="inlineStr">
@@ -17910,6 +18336,7 @@
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr"/>
+      <c r="G252" s="5" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="B253" s="2" t="inlineStr">
@@ -17933,6 +18360,7 @@
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr"/>
+      <c r="G253" s="5" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="B254" s="2" t="inlineStr">
@@ -17956,6 +18384,7 @@
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr"/>
+      <c r="G254" s="5" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="B255" s="2" t="inlineStr">
@@ -17979,6 +18408,7 @@
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr"/>
+      <c r="G255" s="5" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="B256" s="2" t="inlineStr">
@@ -18002,6 +18432,7 @@
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr"/>
+      <c r="G256" s="5" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="B257" s="2" t="inlineStr">
@@ -18025,6 +18456,7 @@
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr"/>
+      <c r="G257" s="5" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="B258" s="2" t="inlineStr">
@@ -18048,6 +18480,7 @@
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr"/>
+      <c r="G258" s="5" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="B259" s="2" t="inlineStr">
@@ -18071,6 +18504,7 @@
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr"/>
+      <c r="G259" s="5" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="B260" s="2" t="inlineStr">
@@ -18094,6 +18528,7 @@
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr"/>
+      <c r="G260" s="5" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="B261" s="2" t="inlineStr">
@@ -18117,6 +18552,7 @@
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr"/>
+      <c r="G261" s="5" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="B262" s="2" t="inlineStr">
@@ -18140,6 +18576,7 @@
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr"/>
+      <c r="G262" s="5" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="B263" s="2" t="inlineStr">
@@ -18163,6 +18600,7 @@
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr"/>
+      <c r="G263" s="5" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="B264" s="2" t="inlineStr">
@@ -18186,6 +18624,7 @@
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr"/>
+      <c r="G264" s="5" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="B265" s="2" t="inlineStr">
@@ -18209,6 +18648,7 @@
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr"/>
+      <c r="G265" s="5" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="B266" s="2" t="inlineStr">
@@ -18232,6 +18672,7 @@
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr"/>
+      <c r="G266" s="5" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="B267" s="2" t="inlineStr">
@@ -18255,6 +18696,7 @@
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr"/>
+      <c r="G267" s="5" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="B268" s="2" t="inlineStr">
@@ -18278,6 +18720,7 @@
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr"/>
+      <c r="G268" s="5" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="B269" s="2" t="inlineStr">
@@ -18301,6 +18744,7 @@
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr"/>
+      <c r="G269" s="5" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="B270" s="2" t="inlineStr">
@@ -18324,6 +18768,7 @@
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr"/>
+      <c r="G270" s="5" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="B271" s="2" t="inlineStr">
@@ -18347,6 +18792,7 @@
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr"/>
+      <c r="G271" s="5" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="B272" s="2" t="inlineStr">
@@ -18370,6 +18816,7 @@
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr"/>
+      <c r="G272" s="5" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="B273" s="2" t="inlineStr">
@@ -18393,6 +18840,7 @@
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr"/>
+      <c r="G273" s="5" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="B274" s="2" t="inlineStr">
@@ -18416,6 +18864,7 @@
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr"/>
+      <c r="G274" s="5" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="B275" s="2" t="inlineStr">
@@ -18439,6 +18888,7 @@
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr"/>
+      <c r="G275" s="5" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="B276" s="2" t="inlineStr">
@@ -18462,6 +18912,7 @@
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr"/>
+      <c r="G276" s="5" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="B277" s="2" t="inlineStr">
@@ -18485,6 +18936,7 @@
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr"/>
+      <c r="G277" s="5" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="B278" s="2" t="inlineStr">
@@ -18508,6 +18960,7 @@
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr"/>
+      <c r="G278" s="5" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="B279" s="2" t="inlineStr">
@@ -18531,6 +18984,7 @@
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr"/>
+      <c r="G279" s="5" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="B280" s="2" t="inlineStr">
@@ -18554,6 +19008,7 @@
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr"/>
+      <c r="G280" s="5" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="B281" s="2" t="inlineStr">
@@ -18577,6 +19032,7 @@
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr"/>
+      <c r="G281" s="5" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="B282" s="2" t="inlineStr">
@@ -18600,6 +19056,7 @@
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr"/>
+      <c r="G282" s="5" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="B283" s="2" t="inlineStr">
@@ -18623,6 +19080,7 @@
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr"/>
+      <c r="G283" s="5" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="B284" s="2" t="inlineStr">
@@ -18646,6 +19104,7 @@
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr"/>
+      <c r="G284" s="5" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="B285" s="2" t="inlineStr">
@@ -18669,6 +19128,7 @@
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr"/>
+      <c r="G285" s="5" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="B286" s="2" t="inlineStr">
@@ -18692,6 +19152,7 @@
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr"/>
+      <c r="G286" s="5" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="B287" s="2" t="inlineStr">
@@ -18715,6 +19176,7 @@
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr"/>
+      <c r="G287" s="5" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="B288" s="2" t="inlineStr">
@@ -18738,6 +19200,7 @@
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr"/>
+      <c r="G288" s="5" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="B289" s="2" t="inlineStr">
@@ -18761,6 +19224,7 @@
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr"/>
+      <c r="G289" s="5" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="B290" s="2" t="inlineStr">
@@ -18784,6 +19248,7 @@
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr"/>
+      <c r="G290" s="5" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="B291" s="2" t="inlineStr">
@@ -18807,6 +19272,7 @@
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr"/>
+      <c r="G291" s="5" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="B292" s="2" t="inlineStr">
@@ -18830,6 +19296,7 @@
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr"/>
+      <c r="G292" s="5" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="B293" s="2" t="inlineStr">
@@ -18853,6 +19320,7 @@
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr"/>
+      <c r="G293" s="5" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="B294" s="2" t="inlineStr">
@@ -18876,6 +19344,7 @@
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr"/>
+      <c r="G294" s="5" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="B295" s="2" t="inlineStr">
@@ -18899,6 +19368,7 @@
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr"/>
+      <c r="G295" s="5" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="B296" s="2" t="inlineStr">
@@ -18922,6 +19392,7 @@
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr"/>
+      <c r="G296" s="5" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="B297" s="2" t="inlineStr">
@@ -18945,6 +19416,7 @@
         </is>
       </c>
       <c r="F297" s="5" t="inlineStr"/>
+      <c r="G297" s="5" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="B298" s="2" t="inlineStr">
@@ -18968,6 +19440,7 @@
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr"/>
+      <c r="G298" s="5" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="B299" s="2" t="inlineStr">
@@ -18991,6 +19464,7 @@
         </is>
       </c>
       <c r="F299" s="5" t="inlineStr"/>
+      <c r="G299" s="5" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="B300" s="2" t="inlineStr">
@@ -19014,6 +19488,7 @@
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr"/>
+      <c r="G300" s="5" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="B301" s="2" t="inlineStr">
@@ -19037,6 +19512,7 @@
         </is>
       </c>
       <c r="F301" s="5" t="inlineStr"/>
+      <c r="G301" s="5" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="B302" s="2" t="inlineStr">
@@ -19060,6 +19536,7 @@
         </is>
       </c>
       <c r="F302" s="5" t="inlineStr"/>
+      <c r="G302" s="5" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="B303" s="2" t="inlineStr">
@@ -19083,6 +19560,7 @@
         </is>
       </c>
       <c r="F303" s="5" t="inlineStr"/>
+      <c r="G303" s="5" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="B304" s="2" t="inlineStr">
@@ -19106,6 +19584,7 @@
         </is>
       </c>
       <c r="F304" s="5" t="inlineStr"/>
+      <c r="G304" s="5" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="B305" s="2" t="inlineStr">
@@ -19129,6 +19608,7 @@
         </is>
       </c>
       <c r="F305" s="5" t="inlineStr"/>
+      <c r="G305" s="5" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="B306" s="2" t="inlineStr">
@@ -19152,6 +19632,7 @@
         </is>
       </c>
       <c r="F306" s="5" t="inlineStr"/>
+      <c r="G306" s="5" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="B307" s="2" t="inlineStr">
@@ -19175,6 +19656,7 @@
         </is>
       </c>
       <c r="F307" s="5" t="inlineStr"/>
+      <c r="G307" s="5" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="B308" s="2" t="inlineStr">
@@ -19198,6 +19680,7 @@
         </is>
       </c>
       <c r="F308" s="5" t="inlineStr"/>
+      <c r="G308" s="5" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="B309" s="2" t="inlineStr">
@@ -19221,6 +19704,7 @@
         </is>
       </c>
       <c r="F309" s="5" t="inlineStr"/>
+      <c r="G309" s="5" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="B310" s="2" t="inlineStr">
@@ -19244,6 +19728,7 @@
         </is>
       </c>
       <c r="F310" s="5" t="inlineStr"/>
+      <c r="G310" s="5" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="B311" s="2" t="inlineStr">
@@ -19267,6 +19752,7 @@
         </is>
       </c>
       <c r="F311" s="5" t="inlineStr"/>
+      <c r="G311" s="5" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="B312" s="2" t="inlineStr">
@@ -19290,6 +19776,7 @@
         </is>
       </c>
       <c r="F312" s="5" t="inlineStr"/>
+      <c r="G312" s="5" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="B313" s="2" t="inlineStr">
@@ -19313,6 +19800,7 @@
         </is>
       </c>
       <c r="F313" s="5" t="inlineStr"/>
+      <c r="G313" s="5" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="B314" s="2" t="inlineStr">
@@ -19336,6 +19824,7 @@
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr"/>
+      <c r="G314" s="5" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="B315" s="2" t="inlineStr">
@@ -19359,6 +19848,7 @@
         </is>
       </c>
       <c r="F315" s="5" t="inlineStr"/>
+      <c r="G315" s="5" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="B316" s="2" t="inlineStr">
@@ -19382,6 +19872,7 @@
         </is>
       </c>
       <c r="F316" s="5" t="inlineStr"/>
+      <c r="G316" s="5" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="B317" s="2" t="inlineStr">
@@ -19405,6 +19896,7 @@
         </is>
       </c>
       <c r="F317" s="5" t="inlineStr"/>
+      <c r="G317" s="5" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="B318" s="2" t="inlineStr">
@@ -19428,6 +19920,7 @@
         </is>
       </c>
       <c r="F318" s="5" t="inlineStr"/>
+      <c r="G318" s="5" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="B319" s="2" t="inlineStr">
@@ -19451,6 +19944,7 @@
         </is>
       </c>
       <c r="F319" s="5" t="inlineStr"/>
+      <c r="G319" s="5" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="B320" s="2" t="inlineStr">
@@ -19474,6 +19968,7 @@
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr"/>
+      <c r="G320" s="5" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="B321" s="2" t="inlineStr">
@@ -19497,6 +19992,7 @@
         </is>
       </c>
       <c r="F321" s="5" t="inlineStr"/>
+      <c r="G321" s="5" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="B322" s="2" t="inlineStr">
@@ -19520,6 +20016,7 @@
         </is>
       </c>
       <c r="F322" s="5" t="inlineStr"/>
+      <c r="G322" s="5" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="B323" s="2" t="inlineStr">
@@ -19543,6 +20040,7 @@
         </is>
       </c>
       <c r="F323" s="5" t="inlineStr"/>
+      <c r="G323" s="5" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="B324" s="2" t="inlineStr">
@@ -19566,6 +20064,7 @@
         </is>
       </c>
       <c r="F324" s="5" t="inlineStr"/>
+      <c r="G324" s="5" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="B325" s="2" t="inlineStr">
@@ -19589,6 +20088,7 @@
         </is>
       </c>
       <c r="F325" s="5" t="inlineStr"/>
+      <c r="G325" s="5" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="B326" s="2" t="inlineStr">
@@ -19612,6 +20112,7 @@
         </is>
       </c>
       <c r="F326" s="5" t="inlineStr"/>
+      <c r="G326" s="5" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="B327" s="2" t="inlineStr">
@@ -19635,6 +20136,7 @@
         </is>
       </c>
       <c r="F327" s="5" t="inlineStr"/>
+      <c r="G327" s="5" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="B328" s="2" t="inlineStr">
@@ -19658,6 +20160,7 @@
         </is>
       </c>
       <c r="F328" s="5" t="inlineStr"/>
+      <c r="G328" s="5" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="B329" s="2" t="inlineStr">
@@ -19681,6 +20184,7 @@
         </is>
       </c>
       <c r="F329" s="5" t="inlineStr"/>
+      <c r="G329" s="5" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="B330" s="2" t="inlineStr">
@@ -19704,6 +20208,7 @@
         </is>
       </c>
       <c r="F330" s="5" t="inlineStr"/>
+      <c r="G330" s="5" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="B331" s="2" t="inlineStr">
@@ -19727,6 +20232,7 @@
         </is>
       </c>
       <c r="F331" s="5" t="inlineStr"/>
+      <c r="G331" s="5" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="B332" s="2" t="inlineStr">
@@ -19750,6 +20256,7 @@
         </is>
       </c>
       <c r="F332" s="5" t="inlineStr"/>
+      <c r="G332" s="5" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="B333" s="2" t="inlineStr">
@@ -19773,6 +20280,7 @@
         </is>
       </c>
       <c r="F333" s="5" t="inlineStr"/>
+      <c r="G333" s="5" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="B334" s="2" t="inlineStr">
@@ -19796,6 +20304,7 @@
         </is>
       </c>
       <c r="F334" s="5" t="inlineStr"/>
+      <c r="G334" s="5" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="B335" s="2" t="inlineStr">
@@ -19819,6 +20328,7 @@
         </is>
       </c>
       <c r="F335" s="5" t="inlineStr"/>
+      <c r="G335" s="5" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="B336" s="2" t="inlineStr">
@@ -19842,6 +20352,7 @@
         </is>
       </c>
       <c r="F336" s="5" t="inlineStr"/>
+      <c r="G336" s="5" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="B337" s="2" t="inlineStr">
@@ -19865,6 +20376,7 @@
         </is>
       </c>
       <c r="F337" s="5" t="inlineStr"/>
+      <c r="G337" s="5" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="B338" s="2" t="inlineStr">
@@ -19888,6 +20400,7 @@
         </is>
       </c>
       <c r="F338" s="5" t="inlineStr"/>
+      <c r="G338" s="5" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="B339" s="2" t="inlineStr">
@@ -19911,6 +20424,7 @@
         </is>
       </c>
       <c r="F339" s="5" t="inlineStr"/>
+      <c r="G339" s="5" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="B340" s="2" t="inlineStr">
@@ -19934,6 +20448,7 @@
         </is>
       </c>
       <c r="F340" s="5" t="inlineStr"/>
+      <c r="G340" s="5" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="B341" s="2" t="inlineStr">
@@ -19957,6 +20472,7 @@
         </is>
       </c>
       <c r="F341" s="5" t="inlineStr"/>
+      <c r="G341" s="5" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="B342" s="2" t="inlineStr">
@@ -19980,6 +20496,7 @@
         </is>
       </c>
       <c r="F342" s="5" t="inlineStr"/>
+      <c r="G342" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19992,7 +20509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -20001,6 +20518,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20034,6 +20552,11 @@
           <t>Default value</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Preprocess rule</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
@@ -20057,6 +20580,7 @@
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
@@ -20076,6 +20600,7 @@
       </c>
       <c r="E3" s="7" t="n"/>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
@@ -20099,6 +20624,7 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
@@ -20122,6 +20648,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
@@ -20145,6 +20672,7 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -20168,6 +20696,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -20191,6 +20720,7 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -20214,6 +20744,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -20237,6 +20768,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -20260,6 +20792,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -20283,6 +20816,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
@@ -20306,6 +20840,7 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -20329,6 +20864,7 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -20352,6 +20888,7 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -20375,6 +20912,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
@@ -20398,6 +20936,7 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
@@ -20421,6 +20960,7 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
@@ -20444,6 +20984,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
@@ -20467,6 +21008,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -20490,6 +21032,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
@@ -20513,6 +21056,7 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
@@ -20536,6 +21080,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
@@ -20559,6 +21104,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/translators/translator_template.xlsx
+++ b/translators/translator_template.xlsx
@@ -11437,7 +11437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11777,12 +11777,12 @@
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>custom_material_quantity_m3</t>
+          <t>lca_service_life</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Material Quantity (m3)</t>
+          <t>Service life</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -11790,9 +11790,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -11801,12 +11801,12 @@
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>custom_material_quantity_m2</t>
+          <t>custom_material_quantity_m3</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Material Quantity (m2)</t>
+          <t>Material Quantity (m3)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -11825,12 +11825,12 @@
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>custom_material_quantity_m</t>
+          <t>custom_material_quantity_m2</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Material Quantity (m)</t>
+          <t>Material Quantity (m2)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -11849,12 +11849,12 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>custom_material_quantity_count</t>
+          <t>custom_material_quantity_m</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Material Quantity (count)</t>
+          <t>Material Quantity (m)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -11873,12 +11873,12 @@
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>custom_material_weight_kg</t>
+          <t>custom_material_quantity_count</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>Material Weight (kg)</t>
+          <t>Material Quantity (count)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -11886,9 +11886,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -11897,12 +11897,12 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>custom_material_density</t>
+          <t>custom_material_weight_kg</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Material Weight (kg)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -11910,13 +11910,37 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>custom_material_density</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/translators/translator_template.xlsx
+++ b/translators/translator_template.xlsx
@@ -12289,7 +12289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G342"/>
+  <dimension ref="A1:G402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -12389,12 +12389,12 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_a4</t>
+          <t>gwp_total_a1</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (A4)</t>
+          <t>Global Warming Potential - Total (A1)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -12413,12 +12413,12 @@
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_a5</t>
+          <t>gwp_total_a2</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (A5)</t>
+          <t>Global Warming Potential - Total (A2)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -12437,12 +12437,12 @@
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_b1</t>
+          <t>gwp_total_a3</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (B1)</t>
+          <t>Global Warming Potential - Total (A3)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -12461,12 +12461,12 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_b2</t>
+          <t>gwp_total_a4</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (B2)</t>
+          <t>Global Warming Potential - Total (A4)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -12485,12 +12485,12 @@
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_b3</t>
+          <t>gwp_total_a5</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (B3)</t>
+          <t>Global Warming Potential - Total (A5)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -12509,12 +12509,12 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_b4</t>
+          <t>gwp_total_b1</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (B4)</t>
+          <t>Global Warming Potential - Total (B1)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -12533,12 +12533,12 @@
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_b5</t>
+          <t>gwp_total_b2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (B5)</t>
+          <t>Global Warming Potential - Total (B2)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -12557,12 +12557,12 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_b6</t>
+          <t>gwp_total_b3</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (B6)</t>
+          <t>Global Warming Potential - Total (B3)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -12581,12 +12581,12 @@
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_c1</t>
+          <t>gwp_total_b4</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (C1)</t>
+          <t>Global Warming Potential - Total (B4)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -12605,12 +12605,12 @@
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_c2</t>
+          <t>gwp_total_b5</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (C2)</t>
+          <t>Global Warming Potential - Total (B5)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -12629,12 +12629,12 @@
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_c3</t>
+          <t>gwp_total_b6</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (C3)</t>
+          <t>Global Warming Potential - Total (B6)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -12653,12 +12653,12 @@
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_c4</t>
+          <t>gwp_total_c1</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (C4)</t>
+          <t>Global Warming Potential - Total (C1)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -12677,12 +12677,12 @@
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_d</t>
+          <t>gwp_total_c2</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (D)</t>
+          <t>Global Warming Potential - Total (C2)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -12701,12 +12701,12 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_d1</t>
+          <t>gwp_total_c3</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (D1)</t>
+          <t>Global Warming Potential - Total (C3)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -12725,12 +12725,12 @@
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>gwp_total_d2</t>
+          <t>gwp_total_c4</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Total (D2)</t>
+          <t>Global Warming Potential - Total (C4)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -12749,12 +12749,12 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>gwp_total</t>
+          <t>gwp_total_d</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Total Global Warming Potential</t>
+          <t>Global Warming Potential - Total (D)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -12762,9 +12762,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Required</t>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -12773,12 +12773,12 @@
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_a1_a3</t>
+          <t>gwp_total_d1</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (A1-A3)</t>
+          <t>Global Warming Potential - Total (D1)</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -12797,12 +12797,12 @@
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_a4</t>
+          <t>gwp_total_d2</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (A4)</t>
+          <t>Global Warming Potential - Total (D2)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -12821,12 +12821,12 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_a5</t>
+          <t>gwp_total</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (A5)</t>
+          <t>Total Global Warming Potential</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -12834,9 +12834,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Recommended</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -12845,12 +12845,12 @@
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_b1</t>
+          <t>gwp_f_a1_a3</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (B1)</t>
+          <t>Global Warming Potential - Fossil (A1-A3)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -12869,12 +12869,12 @@
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_b2</t>
+          <t>gwp_f_a1</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (B2)</t>
+          <t>Global Warming Potential - Fossil (A1)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -12893,12 +12893,12 @@
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_b3</t>
+          <t>gwp_f_a2</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (B3)</t>
+          <t>Global Warming Potential - Fossil (A2)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -12917,12 +12917,12 @@
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_b4</t>
+          <t>gwp_f_a3</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (B4)</t>
+          <t>Global Warming Potential - Fossil (A3)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -12941,12 +12941,12 @@
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_b5</t>
+          <t>gwp_f_a4</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (B5)</t>
+          <t>Global Warming Potential - Fossil (A4)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -12965,12 +12965,12 @@
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_b6</t>
+          <t>gwp_f_a5</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (B6)</t>
+          <t>Global Warming Potential - Fossil (A5)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -12989,12 +12989,12 @@
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_c1</t>
+          <t>gwp_f_b1</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (C1)</t>
+          <t>Global Warming Potential - Fossil (B1)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -13013,12 +13013,12 @@
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_c2</t>
+          <t>gwp_f_b2</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (C2)</t>
+          <t>Global Warming Potential - Fossil (B2)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -13037,12 +13037,12 @@
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_c3</t>
+          <t>gwp_f_b3</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (C3)</t>
+          <t>Global Warming Potential - Fossil (B3)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -13061,12 +13061,12 @@
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_c4</t>
+          <t>gwp_f_b4</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (C4)</t>
+          <t>Global Warming Potential - Fossil (B4)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -13085,12 +13085,12 @@
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_d</t>
+          <t>gwp_f_b5</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (D)</t>
+          <t>Global Warming Potential - Fossil (B5)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -13109,12 +13109,12 @@
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_d1</t>
+          <t>gwp_f_b6</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (D1)</t>
+          <t>Global Warming Potential - Fossil (B6)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -13133,12 +13133,12 @@
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_d2</t>
+          <t>gwp_f_c1</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Fossil (D2)</t>
+          <t>Global Warming Potential - Fossil (C1)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -13157,12 +13157,12 @@
     <row r="36">
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>gwp_f_total</t>
+          <t>gwp_f_c2</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Total Global Warming Potential - Fossil</t>
+          <t>Global Warming Potential - Fossil (C2)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -13181,12 +13181,12 @@
     <row r="37">
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_a1_a3</t>
+          <t>gwp_f_c3</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (A1-A3)</t>
+          <t>Global Warming Potential - Fossil (C3)</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -13205,12 +13205,12 @@
     <row r="38">
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_a4</t>
+          <t>gwp_f_c4</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (A4)</t>
+          <t>Global Warming Potential - Fossil (C4)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -13229,12 +13229,12 @@
     <row r="39">
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_a5</t>
+          <t>gwp_f_d</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (A5)</t>
+          <t>Global Warming Potential - Fossil (D)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -13253,12 +13253,12 @@
     <row r="40">
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_b1</t>
+          <t>gwp_f_d1</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (B1)</t>
+          <t>Global Warming Potential - Fossil (D1)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -13277,12 +13277,12 @@
     <row r="41">
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_b2</t>
+          <t>gwp_f_d2</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (B2)</t>
+          <t>Global Warming Potential - Fossil (D2)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -13301,12 +13301,12 @@
     <row r="42">
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_b3</t>
+          <t>gwp_f_total</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (B3)</t>
+          <t>Total Global Warming Potential - Fossil</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -13325,12 +13325,12 @@
     <row r="43">
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_b4</t>
+          <t>gwp_b_a1_a3</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (B4)</t>
+          <t>Global Warming Potential - Biogenic (A1-A3)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -13349,12 +13349,12 @@
     <row r="44">
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_b5</t>
+          <t>gwp_b_a1</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (B5)</t>
+          <t>Global Warming Potential - Biogenic (A1)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -13373,12 +13373,12 @@
     <row r="45">
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_b6</t>
+          <t>gwp_b_a2</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (B6)</t>
+          <t>Global Warming Potential - Biogenic (A2)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -13397,12 +13397,12 @@
     <row r="46">
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_c1</t>
+          <t>gwp_b_a3</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (C1)</t>
+          <t>Global Warming Potential - Biogenic (A3)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -13421,12 +13421,12 @@
     <row r="47">
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_c2</t>
+          <t>gwp_b_a4</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (C2)</t>
+          <t>Global Warming Potential - Biogenic (A4)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -13445,12 +13445,12 @@
     <row r="48">
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_c3</t>
+          <t>gwp_b_a5</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (C3)</t>
+          <t>Global Warming Potential - Biogenic (A5)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -13469,12 +13469,12 @@
     <row r="49">
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_c4</t>
+          <t>gwp_b_b1</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (C4)</t>
+          <t>Global Warming Potential - Biogenic (B1)</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -13493,12 +13493,12 @@
     <row r="50">
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_d</t>
+          <t>gwp_b_b2</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (D)</t>
+          <t>Global Warming Potential - Biogenic (B2)</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -13517,12 +13517,12 @@
     <row r="51">
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_d1</t>
+          <t>gwp_b_b3</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (D1)</t>
+          <t>Global Warming Potential - Biogenic (B3)</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -13541,12 +13541,12 @@
     <row r="52">
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_d2</t>
+          <t>gwp_b_b4</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Biogenic (D2)</t>
+          <t>Global Warming Potential - Biogenic (B4)</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -13565,12 +13565,12 @@
     <row r="53">
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>gwp_b_total</t>
+          <t>gwp_b_b5</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>Total Global Warming Potential - Biogenic</t>
+          <t>Global Warming Potential - Biogenic (B5)</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -13589,12 +13589,12 @@
     <row r="54">
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_a1_a3</t>
+          <t>gwp_b_b6</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (A1-A3)</t>
+          <t>Global Warming Potential - Biogenic (B6)</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -13613,12 +13613,12 @@
     <row r="55">
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_a4</t>
+          <t>gwp_b_c1</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (A4)</t>
+          <t>Global Warming Potential - Biogenic (C1)</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -13637,12 +13637,12 @@
     <row r="56">
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_a5</t>
+          <t>gwp_b_c2</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (A5)</t>
+          <t>Global Warming Potential - Biogenic (C2)</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -13661,12 +13661,12 @@
     <row r="57">
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_b1</t>
+          <t>gwp_b_c3</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (B1)</t>
+          <t>Global Warming Potential - Biogenic (C3)</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -13685,12 +13685,12 @@
     <row r="58">
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_b2</t>
+          <t>gwp_b_c4</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (B2)</t>
+          <t>Global Warming Potential - Biogenic (C4)</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -13709,12 +13709,12 @@
     <row r="59">
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_b3</t>
+          <t>gwp_b_d</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (B3)</t>
+          <t>Global Warming Potential - Biogenic (D)</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -13733,12 +13733,12 @@
     <row r="60">
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_b4</t>
+          <t>gwp_b_d1</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (B4)</t>
+          <t>Global Warming Potential - Biogenic (D1)</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -13757,12 +13757,12 @@
     <row r="61">
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_b5</t>
+          <t>gwp_b_d2</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (B5)</t>
+          <t>Global Warming Potential - Biogenic (D2)</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -13781,12 +13781,12 @@
     <row r="62">
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_b6</t>
+          <t>gwp_b_total</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (B6)</t>
+          <t>Total Global Warming Potential - Biogenic</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -13805,12 +13805,12 @@
     <row r="63">
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_c1</t>
+          <t>gwp_luc_a1_a3</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (C1)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (A1-A3)</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -13829,12 +13829,12 @@
     <row r="64">
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_c2</t>
+          <t>gwp_luc_a1</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (C2)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (A1)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -13853,12 +13853,12 @@
     <row r="65">
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_c3</t>
+          <t>gwp_luc_a2</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (C3)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (A2)</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -13877,12 +13877,12 @@
     <row r="66">
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_c4</t>
+          <t>gwp_luc_a3</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (C4)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (A3)</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -13901,12 +13901,12 @@
     <row r="67">
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_d</t>
+          <t>gwp_luc_a4</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (D)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (A4)</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -13925,12 +13925,12 @@
     <row r="68">
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_d1</t>
+          <t>gwp_luc_a5</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (D1)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (A5)</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -13949,12 +13949,12 @@
     <row r="69">
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_d2</t>
+          <t>gwp_luc_b1</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Global Warming Potential - Land Use and Land Use Change (D2)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (B1)</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -13973,12 +13973,12 @@
     <row r="70">
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>gwp_luc_total</t>
+          <t>gwp_luc_b2</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Total Global Warming Potential - Land Use and Land Use Change</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (B2)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -13997,12 +13997,12 @@
     <row r="71">
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>odp_a1_a3</t>
+          <t>gwp_luc_b3</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (A1-A3)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (B3)</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -14010,9 +14010,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
@@ -14021,12 +14021,12 @@
     <row r="72">
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>odp_a4</t>
+          <t>gwp_luc_b4</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (A4)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (B4)</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -14034,9 +14034,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
@@ -14045,12 +14045,12 @@
     <row r="73">
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>odp_a5</t>
+          <t>gwp_luc_b5</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (A5)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (B5)</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -14058,9 +14058,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
@@ -14069,12 +14069,12 @@
     <row r="74">
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>odp_b1</t>
+          <t>gwp_luc_b6</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (B1)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (B6)</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -14082,9 +14082,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
@@ -14093,12 +14093,12 @@
     <row r="75">
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>odp_b2</t>
+          <t>gwp_luc_c1</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (B2)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (C1)</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -14106,9 +14106,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
@@ -14117,12 +14117,12 @@
     <row r="76">
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>odp_b3</t>
+          <t>gwp_luc_c2</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (B3)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (C2)</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -14130,9 +14130,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
@@ -14141,12 +14141,12 @@
     <row r="77">
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>odp_b4</t>
+          <t>gwp_luc_c3</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (B4)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (C3)</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -14154,9 +14154,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
@@ -14165,12 +14165,12 @@
     <row r="78">
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>odp_b5</t>
+          <t>gwp_luc_c4</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (B5)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (C4)</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -14178,9 +14178,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
@@ -14189,12 +14189,12 @@
     <row r="79">
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>odp_b6</t>
+          <t>gwp_luc_d</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (B6)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (D)</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -14202,9 +14202,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
@@ -14213,12 +14213,12 @@
     <row r="80">
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>odp_c1</t>
+          <t>gwp_luc_d1</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (C1)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (D1)</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -14226,9 +14226,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
@@ -14237,12 +14237,12 @@
     <row r="81">
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>odp_c2</t>
+          <t>gwp_luc_d2</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (C2)</t>
+          <t>Global Warming Potential - Land Use and Land Use Change (D2)</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -14250,9 +14250,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
@@ -14261,12 +14261,12 @@
     <row r="82">
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>odp_c3</t>
+          <t>gwp_luc_total</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (C3)</t>
+          <t>Total Global Warming Potential - Land Use and Land Use Change</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -14274,9 +14274,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
@@ -14285,12 +14285,12 @@
     <row r="83">
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>odp_c4</t>
+          <t>odp_a1_a3</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (C4)</t>
+          <t>Ozone Depletion Potential (A1-A3)</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -14309,12 +14309,12 @@
     <row r="84">
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>odp_d</t>
+          <t>odp_a1</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (D)</t>
+          <t>Ozone Depletion Potential (A1)</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -14333,12 +14333,12 @@
     <row r="85">
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>odp_d1</t>
+          <t>odp_a2</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (D1)</t>
+          <t>Ozone Depletion Potential (A2)</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -14357,12 +14357,12 @@
     <row r="86">
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>odp_d2</t>
+          <t>odp_a3</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Ozone Depletion Potential (D2)</t>
+          <t>Ozone Depletion Potential (A3)</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -14381,12 +14381,12 @@
     <row r="87">
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>odp_total</t>
+          <t>odp_a4</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>Total Ozone Depletion Potential</t>
+          <t>Ozone Depletion Potential (A4)</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -14405,12 +14405,12 @@
     <row r="88">
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ap_a1_a3</t>
+          <t>odp_a5</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (A1-A3)</t>
+          <t>Ozone Depletion Potential (A5)</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -14429,12 +14429,12 @@
     <row r="89">
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ap_a4</t>
+          <t>odp_b1</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (A4)</t>
+          <t>Ozone Depletion Potential (B1)</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -14453,12 +14453,12 @@
     <row r="90">
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ap_a5</t>
+          <t>odp_b2</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (A5)</t>
+          <t>Ozone Depletion Potential (B2)</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -14477,12 +14477,12 @@
     <row r="91">
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ap_b1</t>
+          <t>odp_b3</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (B1)</t>
+          <t>Ozone Depletion Potential (B3)</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -14501,12 +14501,12 @@
     <row r="92">
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ap_b2</t>
+          <t>odp_b4</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (B2)</t>
+          <t>Ozone Depletion Potential (B4)</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -14525,12 +14525,12 @@
     <row r="93">
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ap_b3</t>
+          <t>odp_b5</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (B3)</t>
+          <t>Ozone Depletion Potential (B5)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -14549,12 +14549,12 @@
     <row r="94">
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ap_b4</t>
+          <t>odp_b6</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (B4)</t>
+          <t>Ozone Depletion Potential (B6)</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -14573,12 +14573,12 @@
     <row r="95">
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ap_b5</t>
+          <t>odp_c1</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (B5)</t>
+          <t>Ozone Depletion Potential (C1)</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -14597,12 +14597,12 @@
     <row r="96">
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ap_b6</t>
+          <t>odp_c2</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (B6)</t>
+          <t>Ozone Depletion Potential (C2)</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -14621,12 +14621,12 @@
     <row r="97">
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>ap_c1</t>
+          <t>odp_c3</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (C1)</t>
+          <t>Ozone Depletion Potential (C3)</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -14645,12 +14645,12 @@
     <row r="98">
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>ap_c2</t>
+          <t>odp_c4</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (C2)</t>
+          <t>Ozone Depletion Potential (C4)</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -14669,12 +14669,12 @@
     <row r="99">
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>ap_c3</t>
+          <t>odp_d</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (C3)</t>
+          <t>Ozone Depletion Potential (D)</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -14693,12 +14693,12 @@
     <row r="100">
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>ap_c4</t>
+          <t>odp_d1</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (C4)</t>
+          <t>Ozone Depletion Potential (D1)</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -14717,12 +14717,12 @@
     <row r="101">
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>ap_d</t>
+          <t>odp_d2</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (D)</t>
+          <t>Ozone Depletion Potential (D2)</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -14741,12 +14741,12 @@
     <row r="102">
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>ap_d1</t>
+          <t>odp_total</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (D1)</t>
+          <t>Total Ozone Depletion Potential</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -14765,12 +14765,12 @@
     <row r="103">
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>ap_d2</t>
+          <t>ap_a1_a3</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Acidification Potential (D2)</t>
+          <t>Acidification Potential (A1-A3)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -14789,12 +14789,12 @@
     <row r="104">
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>ap_total</t>
+          <t>ap_a1</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>Total Acidification Potential</t>
+          <t>Acidification Potential (A1)</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -14813,12 +14813,12 @@
     <row r="105">
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>ep_a1_a3</t>
+          <t>ap_a2</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (A1-A3)</t>
+          <t>Acidification Potential (A2)</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -14837,12 +14837,12 @@
     <row r="106">
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>ep_a4</t>
+          <t>ap_a3</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (A4)</t>
+          <t>Acidification Potential (A3)</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -14861,12 +14861,12 @@
     <row r="107">
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>ep_a5</t>
+          <t>ap_a4</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (A5)</t>
+          <t>Acidification Potential (A4)</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -14885,12 +14885,12 @@
     <row r="108">
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>ep_b1</t>
+          <t>ap_a5</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (B1)</t>
+          <t>Acidification Potential (A5)</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -14909,12 +14909,12 @@
     <row r="109">
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>ep_b2</t>
+          <t>ap_b1</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (B2)</t>
+          <t>Acidification Potential (B1)</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -14933,12 +14933,12 @@
     <row r="110">
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>ep_b3</t>
+          <t>ap_b2</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (B3)</t>
+          <t>Acidification Potential (B2)</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -14957,12 +14957,12 @@
     <row r="111">
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>ep_b4</t>
+          <t>ap_b3</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (B4)</t>
+          <t>Acidification Potential (B3)</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -14981,12 +14981,12 @@
     <row r="112">
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>ep_b5</t>
+          <t>ap_b4</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (B5)</t>
+          <t>Acidification Potential (B4)</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -15005,12 +15005,12 @@
     <row r="113">
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>ep_b6</t>
+          <t>ap_b5</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (B6)</t>
+          <t>Acidification Potential (B5)</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -15029,12 +15029,12 @@
     <row r="114">
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>ep_c1</t>
+          <t>ap_b6</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (C1)</t>
+          <t>Acidification Potential (B6)</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -15053,12 +15053,12 @@
     <row r="115">
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>ep_c2</t>
+          <t>ap_c1</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (C2)</t>
+          <t>Acidification Potential (C1)</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -15077,12 +15077,12 @@
     <row r="116">
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>ep_c3</t>
+          <t>ap_c2</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (C3)</t>
+          <t>Acidification Potential (C2)</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -15101,12 +15101,12 @@
     <row r="117">
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>ep_c4</t>
+          <t>ap_c3</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (C4)</t>
+          <t>Acidification Potential (C3)</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -15125,12 +15125,12 @@
     <row r="118">
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>ep_d</t>
+          <t>ap_c4</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (D)</t>
+          <t>Acidification Potential (C4)</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -15149,12 +15149,12 @@
     <row r="119">
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ep_d1</t>
+          <t>ap_d</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (D1)</t>
+          <t>Acidification Potential (D)</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -15173,12 +15173,12 @@
     <row r="120">
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>ep_d2</t>
+          <t>ap_d1</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential (D2)</t>
+          <t>Acidification Potential (D1)</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -15197,12 +15197,12 @@
     <row r="121">
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>ep_total</t>
+          <t>ap_d2</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>Total Eutrophication Potential</t>
+          <t>Acidification Potential (D2)</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -15221,12 +15221,12 @@
     <row r="122">
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>ep_af_a1_a3</t>
+          <t>ap_total</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (A1-A3)</t>
+          <t>Total Acidification Potential</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -15245,12 +15245,12 @@
     <row r="123">
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>ep_af_a4</t>
+          <t>ep_a1_a3</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (A4)</t>
+          <t>Eutrophication Potential (A1-A3)</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -15269,12 +15269,12 @@
     <row r="124">
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>ep_af_a5</t>
+          <t>ep_a1</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (A5)</t>
+          <t>Eutrophication Potential (A1)</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -15293,12 +15293,12 @@
     <row r="125">
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>ep_af_b1</t>
+          <t>ep_a2</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (B1)</t>
+          <t>Eutrophication Potential (A2)</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -15317,12 +15317,12 @@
     <row r="126">
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>ep_af_b2</t>
+          <t>ep_a3</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (B2)</t>
+          <t>Eutrophication Potential (A3)</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -15341,12 +15341,12 @@
     <row r="127">
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>ep_af_b3</t>
+          <t>ep_a4</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (B3)</t>
+          <t>Eutrophication Potential (A4)</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -15365,12 +15365,12 @@
     <row r="128">
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>ep_af_b4</t>
+          <t>ep_a5</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (B4)</t>
+          <t>Eutrophication Potential (A5)</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -15389,12 +15389,12 @@
     <row r="129">
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>ep_af_b5</t>
+          <t>ep_b1</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (B5)</t>
+          <t>Eutrophication Potential (B1)</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -15413,12 +15413,12 @@
     <row r="130">
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>ep_af_b6</t>
+          <t>ep_b2</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (B6)</t>
+          <t>Eutrophication Potential (B2)</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -15437,12 +15437,12 @@
     <row r="131">
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>ep_af_c1</t>
+          <t>ep_b3</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (C1)</t>
+          <t>Eutrophication Potential (B3)</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -15461,12 +15461,12 @@
     <row r="132">
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>ep_af_c2</t>
+          <t>ep_b4</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (C2)</t>
+          <t>Eutrophication Potential (B4)</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -15485,12 +15485,12 @@
     <row r="133">
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>ep_af_c3</t>
+          <t>ep_b5</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (C3)</t>
+          <t>Eutrophication Potential (B5)</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -15509,12 +15509,12 @@
     <row r="134">
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>ep_af_c4</t>
+          <t>ep_b6</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (C4)</t>
+          <t>Eutrophication Potential (B6)</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -15533,12 +15533,12 @@
     <row r="135">
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>ep_af_d</t>
+          <t>ep_c1</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (D)</t>
+          <t>Eutrophication Potential (C1)</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -15557,12 +15557,12 @@
     <row r="136">
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>ep_af_d1</t>
+          <t>ep_c2</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (D1)</t>
+          <t>Eutrophication Potential (C2)</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -15581,12 +15581,12 @@
     <row r="137">
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>ep_af_d2</t>
+          <t>ep_c3</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Freshwater (D2)</t>
+          <t>Eutrophication Potential (C3)</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -15605,12 +15605,12 @@
     <row r="138">
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ep_af_total</t>
+          <t>ep_c4</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Total Eutrophication Potential - Aquatic Freshwater</t>
+          <t>Eutrophication Potential (C4)</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -15629,12 +15629,12 @@
     <row r="139">
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ep_am_a1_a3</t>
+          <t>ep_d</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (A1-A3)</t>
+          <t>Eutrophication Potential (D)</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -15653,12 +15653,12 @@
     <row r="140">
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>ep_am_a4</t>
+          <t>ep_d1</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (A4)</t>
+          <t>Eutrophication Potential (D1)</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -15677,12 +15677,12 @@
     <row r="141">
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>ep_am_a5</t>
+          <t>ep_d2</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (A5)</t>
+          <t>Eutrophication Potential (D2)</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -15701,12 +15701,12 @@
     <row r="142">
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>ep_am_b1</t>
+          <t>ep_total</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (B1)</t>
+          <t>Total Eutrophication Potential</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -15725,12 +15725,12 @@
     <row r="143">
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>ep_am_b2</t>
+          <t>ep_af_a1_a3</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (B2)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (A1-A3)</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -15749,12 +15749,12 @@
     <row r="144">
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>ep_am_b3</t>
+          <t>ep_af_a1</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (B3)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (A1)</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -15773,12 +15773,12 @@
     <row r="145">
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>ep_am_b4</t>
+          <t>ep_af_a2</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (B4)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (A2)</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -15797,12 +15797,12 @@
     <row r="146">
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>ep_am_b5</t>
+          <t>ep_af_a3</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (B5)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (A3)</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -15821,12 +15821,12 @@
     <row r="147">
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ep_am_b6</t>
+          <t>ep_af_a4</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (B6)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (A4)</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -15845,12 +15845,12 @@
     <row r="148">
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>ep_am_c1</t>
+          <t>ep_af_a5</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (C1)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (A5)</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -15869,12 +15869,12 @@
     <row r="149">
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>ep_am_c2</t>
+          <t>ep_af_b1</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (C2)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (B1)</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -15893,12 +15893,12 @@
     <row r="150">
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>ep_am_c3</t>
+          <t>ep_af_b2</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (C3)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (B2)</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -15917,12 +15917,12 @@
     <row r="151">
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>ep_am_c4</t>
+          <t>ep_af_b3</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (C4)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (B3)</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -15941,12 +15941,12 @@
     <row r="152">
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>ep_am_d</t>
+          <t>ep_af_b4</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (D)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (B4)</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -15965,12 +15965,12 @@
     <row r="153">
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>ep_am_d1</t>
+          <t>ep_af_b5</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (D1)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (B5)</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -15989,12 +15989,12 @@
     <row r="154">
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>ep_am_d2</t>
+          <t>ep_af_b6</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Aquatic Marine (D2)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (B6)</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -16013,12 +16013,12 @@
     <row r="155">
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>ep_am_total</t>
+          <t>ep_af_c1</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>Total Eutrophication Potential - Aquatic Marine</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (C1)</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -16037,12 +16037,12 @@
     <row r="156">
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>ep_t_a1_a3</t>
+          <t>ep_af_c2</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (A1-A3)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (C2)</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -16061,12 +16061,12 @@
     <row r="157">
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>ep_t_a4</t>
+          <t>ep_af_c3</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (A4)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (C3)</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -16085,12 +16085,12 @@
     <row r="158">
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>ep_t_a5</t>
+          <t>ep_af_c4</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (A5)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (C4)</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -16109,12 +16109,12 @@
     <row r="159">
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>ep_t_b1</t>
+          <t>ep_af_d</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (B1)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (D)</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -16133,12 +16133,12 @@
     <row r="160">
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>ep_t_b2</t>
+          <t>ep_af_d1</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (B2)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (D1)</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -16157,12 +16157,12 @@
     <row r="161">
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>ep_t_b3</t>
+          <t>ep_af_d2</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (B3)</t>
+          <t>Eutrophication Potential - Aquatic Freshwater (D2)</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -16181,12 +16181,12 @@
     <row r="162">
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>ep_t_b4</t>
+          <t>ep_af_total</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (B4)</t>
+          <t>Total Eutrophication Potential - Aquatic Freshwater</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -16205,12 +16205,12 @@
     <row r="163">
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>ep_t_b5</t>
+          <t>ep_am_a1_a3</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (B5)</t>
+          <t>Eutrophication Potential - Aquatic Marine (A1-A3)</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -16229,12 +16229,12 @@
     <row r="164">
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>ep_t_b6</t>
+          <t>ep_am_a1</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (B6)</t>
+          <t>Eutrophication Potential - Aquatic Marine (A1)</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -16253,12 +16253,12 @@
     <row r="165">
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>ep_t_c1</t>
+          <t>ep_am_a2</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (C1)</t>
+          <t>Eutrophication Potential - Aquatic Marine (A2)</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -16277,12 +16277,12 @@
     <row r="166">
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>ep_t_c2</t>
+          <t>ep_am_a3</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (C2)</t>
+          <t>Eutrophication Potential - Aquatic Marine (A3)</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -16301,12 +16301,12 @@
     <row r="167">
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>ep_t_c3</t>
+          <t>ep_am_a4</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (C3)</t>
+          <t>Eutrophication Potential - Aquatic Marine (A4)</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -16325,12 +16325,12 @@
     <row r="168">
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>ep_t_c4</t>
+          <t>ep_am_a5</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (C4)</t>
+          <t>Eutrophication Potential - Aquatic Marine (A5)</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -16349,12 +16349,12 @@
     <row r="169">
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>ep_t_d</t>
+          <t>ep_am_b1</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (D)</t>
+          <t>Eutrophication Potential - Aquatic Marine (B1)</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -16373,12 +16373,12 @@
     <row r="170">
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>ep_t_d1</t>
+          <t>ep_am_b2</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (D1)</t>
+          <t>Eutrophication Potential - Aquatic Marine (B2)</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -16397,12 +16397,12 @@
     <row r="171">
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>ep_t_d2</t>
+          <t>ep_am_b3</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>Eutrophication Potential - Terrestrial (D2)</t>
+          <t>Eutrophication Potential - Aquatic Marine (B3)</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -16421,12 +16421,12 @@
     <row r="172">
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>ep_t_total</t>
+          <t>ep_am_b4</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>Total Eutrophication Potential - Terrestrial</t>
+          <t>Eutrophication Potential - Aquatic Marine (B4)</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -16445,12 +16445,12 @@
     <row r="173">
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>pocp_a1_a3</t>
+          <t>ep_am_b5</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (A1-A3)</t>
+          <t>Eutrophication Potential - Aquatic Marine (B5)</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -16469,12 +16469,12 @@
     <row r="174">
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>pocp_a4</t>
+          <t>ep_am_b6</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (A4)</t>
+          <t>Eutrophication Potential - Aquatic Marine (B6)</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -16493,12 +16493,12 @@
     <row r="175">
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>pocp_a5</t>
+          <t>ep_am_c1</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (A5)</t>
+          <t>Eutrophication Potential - Aquatic Marine (C1)</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -16517,12 +16517,12 @@
     <row r="176">
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>pocp_b1</t>
+          <t>ep_am_c2</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (B1)</t>
+          <t>Eutrophication Potential - Aquatic Marine (C2)</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -16541,12 +16541,12 @@
     <row r="177">
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>pocp_b2</t>
+          <t>ep_am_c3</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (B2)</t>
+          <t>Eutrophication Potential - Aquatic Marine (C3)</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -16565,12 +16565,12 @@
     <row r="178">
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>pocp_b3</t>
+          <t>ep_am_c4</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (B3)</t>
+          <t>Eutrophication Potential - Aquatic Marine (C4)</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -16589,12 +16589,12 @@
     <row r="179">
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>pocp_b4</t>
+          <t>ep_am_d</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (B4)</t>
+          <t>Eutrophication Potential - Aquatic Marine (D)</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -16613,12 +16613,12 @@
     <row r="180">
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>pocp_b5</t>
+          <t>ep_am_d1</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (B5)</t>
+          <t>Eutrophication Potential - Aquatic Marine (D1)</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -16637,12 +16637,12 @@
     <row r="181">
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>pocp_b6</t>
+          <t>ep_am_d2</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (B6)</t>
+          <t>Eutrophication Potential - Aquatic Marine (D2)</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -16661,12 +16661,12 @@
     <row r="182">
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>pocp_c1</t>
+          <t>ep_am_total</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (C1)</t>
+          <t>Total Eutrophication Potential - Aquatic Marine</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -16685,12 +16685,12 @@
     <row r="183">
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>pocp_c2</t>
+          <t>ep_t_a1_a3</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (C2)</t>
+          <t>Eutrophication Potential - Terrestrial (A1-A3)</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -16709,12 +16709,12 @@
     <row r="184">
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>pocp_c3</t>
+          <t>ep_t_a1</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (C3)</t>
+          <t>Eutrophication Potential - Terrestrial (A1)</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -16733,12 +16733,12 @@
     <row r="185">
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>pocp_c4</t>
+          <t>ep_t_a2</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (C4)</t>
+          <t>Eutrophication Potential - Terrestrial (A2)</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -16757,12 +16757,12 @@
     <row r="186">
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>pocp_d</t>
+          <t>ep_t_a3</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (D)</t>
+          <t>Eutrophication Potential - Terrestrial (A3)</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -16781,12 +16781,12 @@
     <row r="187">
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>pocp_d1</t>
+          <t>ep_t_a4</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (D1)</t>
+          <t>Eutrophication Potential - Terrestrial (A4)</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -16805,12 +16805,12 @@
     <row r="188">
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>pocp_d2</t>
+          <t>ep_t_a5</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Creation Potential (D2)</t>
+          <t>Eutrophication Potential - Terrestrial (A5)</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -16829,12 +16829,12 @@
     <row r="189">
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>pocp_total</t>
+          <t>ep_t_b1</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>Total Photochemical Ozone Creation Potential</t>
+          <t>Eutrophication Potential - Terrestrial (B1)</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -16853,12 +16853,12 @@
     <row r="190">
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>sfp_a1_a3</t>
+          <t>ep_t_b2</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (A1-A3)</t>
+          <t>Eutrophication Potential - Terrestrial (B2)</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -16877,12 +16877,12 @@
     <row r="191">
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>sfp_a4</t>
+          <t>ep_t_b3</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (A4)</t>
+          <t>Eutrophication Potential - Terrestrial (B3)</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -16901,12 +16901,12 @@
     <row r="192">
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>sfp_a5</t>
+          <t>ep_t_b4</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (A5)</t>
+          <t>Eutrophication Potential - Terrestrial (B4)</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -16925,12 +16925,12 @@
     <row r="193">
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>sfp_b1</t>
+          <t>ep_t_b5</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (B1)</t>
+          <t>Eutrophication Potential - Terrestrial (B5)</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -16949,12 +16949,12 @@
     <row r="194">
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>sfp_b2</t>
+          <t>ep_t_b6</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (B2)</t>
+          <t>Eutrophication Potential - Terrestrial (B6)</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -16973,12 +16973,12 @@
     <row r="195">
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>sfp_b3</t>
+          <t>ep_t_c1</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (B3)</t>
+          <t>Eutrophication Potential - Terrestrial (C1)</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -16997,12 +16997,12 @@
     <row r="196">
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>sfp_b4</t>
+          <t>ep_t_c2</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (B4)</t>
+          <t>Eutrophication Potential - Terrestrial (C2)</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -17021,12 +17021,12 @@
     <row r="197">
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>sfp_b5</t>
+          <t>ep_t_c3</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (B5)</t>
+          <t>Eutrophication Potential - Terrestrial (C3)</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -17045,12 +17045,12 @@
     <row r="198">
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>sfp_b6</t>
+          <t>ep_t_c4</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (B6)</t>
+          <t>Eutrophication Potential - Terrestrial (C4)</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -17069,12 +17069,12 @@
     <row r="199">
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>sfp_c1</t>
+          <t>ep_t_d</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (C1)</t>
+          <t>Eutrophication Potential - Terrestrial (D)</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -17093,12 +17093,12 @@
     <row r="200">
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>sfp_c2</t>
+          <t>ep_t_d1</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (C2)</t>
+          <t>Eutrophication Potential - Terrestrial (D1)</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -17117,12 +17117,12 @@
     <row r="201">
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>sfp_c3</t>
+          <t>ep_t_d2</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (C3)</t>
+          <t>Eutrophication Potential - Terrestrial (D2)</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -17141,12 +17141,12 @@
     <row r="202">
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>sfp_c4</t>
+          <t>ep_t_total</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (C4)</t>
+          <t>Total Eutrophication Potential - Terrestrial</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -17165,12 +17165,12 @@
     <row r="203">
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>sfp_d</t>
+          <t>pocp_a1_a3</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (D)</t>
+          <t>Photochemical Ozone Creation Potential (A1-A3)</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -17189,12 +17189,12 @@
     <row r="204">
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>sfp_d1</t>
+          <t>pocp_a1</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (D1)</t>
+          <t>Photochemical Ozone Creation Potential (A1)</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -17213,12 +17213,12 @@
     <row r="205">
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>sfp_d2</t>
+          <t>pocp_a2</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>Smog Forming Potential (D2)</t>
+          <t>Photochemical Ozone Creation Potential (A2)</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -17237,12 +17237,12 @@
     <row r="206">
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>sfp_total</t>
+          <t>pocp_a3</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t>Total Smog Forming Potential</t>
+          <t>Photochemical Ozone Creation Potential (A3)</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -17261,12 +17261,12 @@
     <row r="207">
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>pofp_a1_a3</t>
+          <t>pocp_a4</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (A1-A3)</t>
+          <t>Photochemical Ozone Creation Potential (A4)</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -17285,12 +17285,12 @@
     <row r="208">
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>pofp_a4</t>
+          <t>pocp_a5</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (A4)</t>
+          <t>Photochemical Ozone Creation Potential (A5)</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -17309,12 +17309,12 @@
     <row r="209">
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>pofp_a5</t>
+          <t>pocp_b1</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (A5)</t>
+          <t>Photochemical Ozone Creation Potential (B1)</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -17333,12 +17333,12 @@
     <row r="210">
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>pofp_b1</t>
+          <t>pocp_b2</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B1)</t>
+          <t>Photochemical Ozone Creation Potential (B2)</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -17357,12 +17357,12 @@
     <row r="211">
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>pofp_b2</t>
+          <t>pocp_b3</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B2)</t>
+          <t>Photochemical Ozone Creation Potential (B3)</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -17381,12 +17381,12 @@
     <row r="212">
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>pofp_b3</t>
+          <t>pocp_b4</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B3)</t>
+          <t>Photochemical Ozone Creation Potential (B4)</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -17405,12 +17405,12 @@
     <row r="213">
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>pofp_b4</t>
+          <t>pocp_b5</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B4)</t>
+          <t>Photochemical Ozone Creation Potential (B5)</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -17429,12 +17429,12 @@
     <row r="214">
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>pofp_b5</t>
+          <t>pocp_b6</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B5)</t>
+          <t>Photochemical Ozone Creation Potential (B6)</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -17453,12 +17453,12 @@
     <row r="215">
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>pofp_b6</t>
+          <t>pocp_c1</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (B6)</t>
+          <t>Photochemical Ozone Creation Potential (C1)</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -17477,12 +17477,12 @@
     <row r="216">
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>pofp_c1</t>
+          <t>pocp_c2</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (C1)</t>
+          <t>Photochemical Ozone Creation Potential (C2)</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -17501,12 +17501,12 @@
     <row r="217">
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>pofp_c2</t>
+          <t>pocp_c3</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (C2)</t>
+          <t>Photochemical Ozone Creation Potential (C3)</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -17525,12 +17525,12 @@
     <row r="218">
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>pofp_c3</t>
+          <t>pocp_c4</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (C3)</t>
+          <t>Photochemical Ozone Creation Potential (C4)</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -17549,12 +17549,12 @@
     <row r="219">
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>pofp_c4</t>
+          <t>pocp_d</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (C4)</t>
+          <t>Photochemical Ozone Creation Potential (D)</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -17573,12 +17573,12 @@
     <row r="220">
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>pofp_d</t>
+          <t>pocp_d1</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (D)</t>
+          <t>Photochemical Ozone Creation Potential (D1)</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -17597,12 +17597,12 @@
     <row r="221">
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>pofp_d1</t>
+          <t>pocp_d2</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (D1)</t>
+          <t>Photochemical Ozone Creation Potential (D2)</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -17621,12 +17621,12 @@
     <row r="222">
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>pofp_d2</t>
+          <t>pocp_total</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>Photochemical Ozone Formation Potential (D2)</t>
+          <t>Total Photochemical Ozone Creation Potential</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -17645,12 +17645,12 @@
     <row r="223">
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>pofp_total</t>
+          <t>sfp_a1_a3</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>Total Photochemical Ozone Formation Potential</t>
+          <t>Smog Forming Potential (A1-A3)</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -17669,12 +17669,12 @@
     <row r="224">
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>adpmm_a1_a3</t>
+          <t>sfp_a1</t>
         </is>
       </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (A1-A3)</t>
+          <t>Smog Forming Potential (A1)</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -17693,12 +17693,12 @@
     <row r="225">
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>adpmm_a4</t>
+          <t>sfp_a2</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (A4)</t>
+          <t>Smog Forming Potential (A2)</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -17717,12 +17717,12 @@
     <row r="226">
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>adpmm_a5</t>
+          <t>sfp_a3</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (A5)</t>
+          <t>Smog Forming Potential (A3)</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -17741,12 +17741,12 @@
     <row r="227">
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>adpmm_b1</t>
+          <t>sfp_a4</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (B1)</t>
+          <t>Smog Forming Potential (A4)</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -17765,12 +17765,12 @@
     <row r="228">
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>adpmm_b2</t>
+          <t>sfp_a5</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (B2)</t>
+          <t>Smog Forming Potential (A5)</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -17789,12 +17789,12 @@
     <row r="229">
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>adpmm_b3</t>
+          <t>sfp_b1</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (B3)</t>
+          <t>Smog Forming Potential (B1)</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -17813,12 +17813,12 @@
     <row r="230">
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>adpmm_b4</t>
+          <t>sfp_b2</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (B4)</t>
+          <t>Smog Forming Potential (B2)</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -17837,12 +17837,12 @@
     <row r="231">
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>adpmm_b5</t>
+          <t>sfp_b3</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (B5)</t>
+          <t>Smog Forming Potential (B3)</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -17861,12 +17861,12 @@
     <row r="232">
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>adpmm_b6</t>
+          <t>sfp_b4</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (B6)</t>
+          <t>Smog Forming Potential (B4)</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -17885,12 +17885,12 @@
     <row r="233">
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>adpmm_c1</t>
+          <t>sfp_b5</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (C1)</t>
+          <t>Smog Forming Potential (B5)</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -17909,12 +17909,12 @@
     <row r="234">
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>adpmm_c2</t>
+          <t>sfp_b6</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (C2)</t>
+          <t>Smog Forming Potential (B6)</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -17933,12 +17933,12 @@
     <row r="235">
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>adpmm_c3</t>
+          <t>sfp_c1</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (C3)</t>
+          <t>Smog Forming Potential (C1)</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -17957,12 +17957,12 @@
     <row r="236">
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>adpmm_c4</t>
+          <t>sfp_c2</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (C4)</t>
+          <t>Smog Forming Potential (C2)</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -17981,12 +17981,12 @@
     <row r="237">
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>adpmm_d</t>
+          <t>sfp_c3</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (D)</t>
+          <t>Smog Forming Potential (C3)</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -18005,12 +18005,12 @@
     <row r="238">
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>adpmm_d1</t>
+          <t>sfp_c4</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (D1)</t>
+          <t>Smog Forming Potential (C4)</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -18029,12 +18029,12 @@
     <row r="239">
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>adpmm_d2</t>
+          <t>sfp_d</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Minerals and Metals) (D2)</t>
+          <t>Smog Forming Potential (D)</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -18053,12 +18053,12 @@
     <row r="240">
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>adpmm_total</t>
+          <t>sfp_d1</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>Total Abiotic Depletion Potential (Minerals and Metals)</t>
+          <t>Smog Forming Potential (D1)</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -18077,12 +18077,12 @@
     <row r="241">
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>adpf_a1_a3</t>
+          <t>sfp_d2</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (A1-A3)</t>
+          <t>Smog Forming Potential (D2)</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -18101,12 +18101,12 @@
     <row r="242">
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>adpf_a4</t>
+          <t>sfp_total</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (A4)</t>
+          <t>Total Smog Forming Potential</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -18125,12 +18125,12 @@
     <row r="243">
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>adpf_a5</t>
+          <t>pofp_a1_a3</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (A5)</t>
+          <t>Photochemical Ozone Formation Potential (A1-A3)</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -18149,12 +18149,12 @@
     <row r="244">
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>adpf_b1</t>
+          <t>pofp_a1</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (B1)</t>
+          <t>Photochemical Ozone Formation Potential (A1)</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -18173,12 +18173,12 @@
     <row r="245">
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>adpf_b2</t>
+          <t>pofp_a2</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (B2)</t>
+          <t>Photochemical Ozone Formation Potential (A2)</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -18197,12 +18197,12 @@
     <row r="246">
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>adpf_b3</t>
+          <t>pofp_a3</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (B3)</t>
+          <t>Photochemical Ozone Formation Potential (A3)</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -18221,12 +18221,12 @@
     <row r="247">
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>adpf_b4</t>
+          <t>pofp_a4</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (B4)</t>
+          <t>Photochemical Ozone Formation Potential (A4)</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -18245,12 +18245,12 @@
     <row r="248">
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>adpf_b5</t>
+          <t>pofp_a5</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (B5)</t>
+          <t>Photochemical Ozone Formation Potential (A5)</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -18269,12 +18269,12 @@
     <row r="249">
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>adpf_b6</t>
+          <t>pofp_b1</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (B6)</t>
+          <t>Photochemical Ozone Formation Potential (B1)</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -18293,12 +18293,12 @@
     <row r="250">
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>adpf_c1</t>
+          <t>pofp_b2</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (C1)</t>
+          <t>Photochemical Ozone Formation Potential (B2)</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -18317,12 +18317,12 @@
     <row r="251">
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>adpf_c2</t>
+          <t>pofp_b3</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (C2)</t>
+          <t>Photochemical Ozone Formation Potential (B3)</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -18341,12 +18341,12 @@
     <row r="252">
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>adpf_c3</t>
+          <t>pofp_b4</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (C3)</t>
+          <t>Photochemical Ozone Formation Potential (B4)</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -18365,12 +18365,12 @@
     <row r="253">
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>adpf_c4</t>
+          <t>pofp_b5</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (C4)</t>
+          <t>Photochemical Ozone Formation Potential (B5)</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -18389,12 +18389,12 @@
     <row r="254">
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>adpf_d</t>
+          <t>pofp_b6</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (D)</t>
+          <t>Photochemical Ozone Formation Potential (B6)</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -18413,12 +18413,12 @@
     <row r="255">
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>adpf_d1</t>
+          <t>pofp_c1</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (D1)</t>
+          <t>Photochemical Ozone Formation Potential (C1)</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -18437,12 +18437,12 @@
     <row r="256">
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>adpf_d2</t>
+          <t>pofp_c2</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t>Abiotic Depletion Potential (Fossil Fuels) (D2)</t>
+          <t>Photochemical Ozone Formation Potential (C2)</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -18461,12 +18461,12 @@
     <row r="257">
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>adpf_total</t>
+          <t>pofp_c3</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t>Total Abiotic Depletion Potential (Fossil Fuels)</t>
+          <t>Photochemical Ozone Formation Potential (C3)</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -18485,12 +18485,12 @@
     <row r="258">
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>wdp_a1_a3</t>
+          <t>pofp_c4</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (A1-A3)</t>
+          <t>Photochemical Ozone Formation Potential (C4)</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -18509,12 +18509,12 @@
     <row r="259">
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>wdp_a4</t>
+          <t>pofp_d</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (A4)</t>
+          <t>Photochemical Ozone Formation Potential (D)</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -18533,12 +18533,12 @@
     <row r="260">
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>wdp_a5</t>
+          <t>pofp_d1</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (A5)</t>
+          <t>Photochemical Ozone Formation Potential (D1)</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -18557,12 +18557,12 @@
     <row r="261">
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>wdp_b1</t>
+          <t>pofp_d2</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (B1)</t>
+          <t>Photochemical Ozone Formation Potential (D2)</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -18581,12 +18581,12 @@
     <row r="262">
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>wdp_b2</t>
+          <t>pofp_total</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (B2)</t>
+          <t>Total Photochemical Ozone Formation Potential</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -18605,12 +18605,12 @@
     <row r="263">
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>wdp_b3</t>
+          <t>adpmm_a1_a3</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (B3)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (A1-A3)</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -18629,12 +18629,12 @@
     <row r="264">
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>wdp_b4</t>
+          <t>adpmm_a1</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (B4)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (A1)</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -18653,12 +18653,12 @@
     <row r="265">
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>wdp_b5</t>
+          <t>adpmm_a2</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (B5)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (A2)</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -18677,12 +18677,12 @@
     <row r="266">
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>wdp_b6</t>
+          <t>adpmm_a3</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (B6)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (A3)</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -18701,12 +18701,12 @@
     <row r="267">
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>wdp_c1</t>
+          <t>adpmm_a4</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (C1)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (A4)</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -18725,12 +18725,12 @@
     <row r="268">
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>wdp_c2</t>
+          <t>adpmm_a5</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (C2)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (A5)</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -18749,12 +18749,12 @@
     <row r="269">
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>wdp_c3</t>
+          <t>adpmm_b1</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (C3)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (B1)</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -18773,12 +18773,12 @@
     <row r="270">
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>wdp_c4</t>
+          <t>adpmm_b2</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (C4)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (B2)</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -18797,12 +18797,12 @@
     <row r="271">
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>wdp_d</t>
+          <t>adpmm_b3</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (D)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (B3)</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -18821,12 +18821,12 @@
     <row r="272">
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>wdp_d1</t>
+          <t>adpmm_b4</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (D1)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (B4)</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -18845,12 +18845,12 @@
     <row r="273">
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>wdp_d2</t>
+          <t>adpmm_b5</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>Water Depletion Potential (D2)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (B5)</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -18869,12 +18869,12 @@
     <row r="274">
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>wdp_total</t>
+          <t>adpmm_b6</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t>Total Water Depletion Potential</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (B6)</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -18893,12 +18893,12 @@
     <row r="275">
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>pere_a1_a3</t>
+          <t>adpmm_c1</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (A1-A3)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (C1)</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -18917,12 +18917,12 @@
     <row r="276">
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>pere_a4</t>
+          <t>adpmm_c2</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (A4)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (C2)</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -18941,12 +18941,12 @@
     <row r="277">
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>pere_a5</t>
+          <t>adpmm_c3</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (A5)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (C3)</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -18965,12 +18965,12 @@
     <row r="278">
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>pere_b1</t>
+          <t>adpmm_c4</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (B1)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (C4)</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -18989,12 +18989,12 @@
     <row r="279">
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>pere_b2</t>
+          <t>adpmm_d</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (B2)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (D)</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -19013,12 +19013,12 @@
     <row r="280">
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>pere_b3</t>
+          <t>adpmm_d1</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (B3)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (D1)</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -19037,12 +19037,12 @@
     <row r="281">
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>pere_b4</t>
+          <t>adpmm_d2</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (B4)</t>
+          <t>Abiotic Depletion Potential (Minerals and Metals) (D2)</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -19061,12 +19061,12 @@
     <row r="282">
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>pere_b5</t>
+          <t>adpmm_total</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (B5)</t>
+          <t>Total Abiotic Depletion Potential (Minerals and Metals)</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -19085,12 +19085,12 @@
     <row r="283">
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>pere_b6</t>
+          <t>adpf_a1_a3</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (B6)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (A1-A3)</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -19109,12 +19109,12 @@
     <row r="284">
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>pere_c1</t>
+          <t>adpf_a1</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (C1)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (A1)</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -19133,12 +19133,12 @@
     <row r="285">
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>pere_c2</t>
+          <t>adpf_a2</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (C2)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (A2)</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -19157,12 +19157,12 @@
     <row r="286">
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>pere_c3</t>
+          <t>adpf_a3</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (C3)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (A3)</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -19181,12 +19181,12 @@
     <row r="287">
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>pere_c4</t>
+          <t>adpf_a4</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (C4)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (A4)</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -19205,12 +19205,12 @@
     <row r="288">
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>pere_d</t>
+          <t>adpf_a5</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (D)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (A5)</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -19229,12 +19229,12 @@
     <row r="289">
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>pere_d1</t>
+          <t>adpf_b1</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (D1)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (B1)</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -19253,12 +19253,12 @@
     <row r="290">
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>pere_d2</t>
+          <t>adpf_b2</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable (Energy resources) (D2)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (B2)</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -19277,12 +19277,12 @@
     <row r="291">
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>pere_total</t>
+          <t>adpf_b3</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
-          <t>Total Primary Energy Renewable (Energy resources)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (B3)</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -19301,12 +19301,12 @@
     <row r="292">
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>penre_a1_a3</t>
+          <t>adpf_b4</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (A1-A3)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (B4)</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -19325,12 +19325,12 @@
     <row r="293">
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>penre_a4</t>
+          <t>adpf_b5</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (A4)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (B5)</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -19349,12 +19349,12 @@
     <row r="294">
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>penre_a5</t>
+          <t>adpf_b6</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (A5)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (B6)</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -19373,12 +19373,12 @@
     <row r="295">
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>penre_b1</t>
+          <t>adpf_c1</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (B1)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (C1)</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -19397,12 +19397,12 @@
     <row r="296">
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>penre_b2</t>
+          <t>adpf_c2</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (B2)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (C2)</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -19421,12 +19421,12 @@
     <row r="297">
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>penre_b3</t>
+          <t>adpf_c3</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (B3)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (C3)</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -19445,12 +19445,12 @@
     <row r="298">
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>penre_b4</t>
+          <t>adpf_c4</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (B4)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (C4)</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -19469,12 +19469,12 @@
     <row r="299">
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>penre_b5</t>
+          <t>adpf_d</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (B5)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (D)</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -19493,12 +19493,12 @@
     <row r="300">
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>penre_b6</t>
+          <t>adpf_d1</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (B6)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (D1)</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -19517,12 +19517,12 @@
     <row r="301">
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>penre_c1</t>
+          <t>adpf_d2</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (C1)</t>
+          <t>Abiotic Depletion Potential (Fossil Fuels) (D2)</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -19541,12 +19541,12 @@
     <row r="302">
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>penre_c2</t>
+          <t>adpf_total</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (C2)</t>
+          <t>Total Abiotic Depletion Potential (Fossil Fuels)</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
@@ -19565,12 +19565,12 @@
     <row r="303">
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>penre_c3</t>
+          <t>wdp_a1_a3</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (C3)</t>
+          <t>Water Depletion Potential (A1-A3)</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
@@ -19589,12 +19589,12 @@
     <row r="304">
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>penre_c4</t>
+          <t>wdp_a1</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (C4)</t>
+          <t>Water Depletion Potential (A1)</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
@@ -19613,12 +19613,12 @@
     <row r="305">
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>penre_d</t>
+          <t>wdp_a2</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (D)</t>
+          <t>Water Depletion Potential (A2)</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
@@ -19637,12 +19637,12 @@
     <row r="306">
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>penre_d1</t>
+          <t>wdp_a3</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (D1)</t>
+          <t>Water Depletion Potential (A3)</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
@@ -19661,12 +19661,12 @@
     <row r="307">
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>penre_d2</t>
+          <t>wdp_a4</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable (Energy resources) (D2)</t>
+          <t>Water Depletion Potential (A4)</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
@@ -19685,12 +19685,12 @@
     <row r="308">
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>penre_total</t>
+          <t>wdp_a5</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t>Total Primary Energy Non-Renewable (Energy resources)</t>
+          <t>Water Depletion Potential (A5)</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
@@ -19709,12 +19709,12 @@
     <row r="309">
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>pert_a1_a3</t>
+          <t>wdp_b1</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (A1-A3)</t>
+          <t>Water Depletion Potential (B1)</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
@@ -19733,12 +19733,12 @@
     <row r="310">
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>pert_a4</t>
+          <t>wdp_b2</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (A4)</t>
+          <t>Water Depletion Potential (B2)</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -19757,12 +19757,12 @@
     <row r="311">
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>pert_a5</t>
+          <t>wdp_b3</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (A5)</t>
+          <t>Water Depletion Potential (B3)</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
@@ -19781,12 +19781,12 @@
     <row r="312">
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>pert_b1</t>
+          <t>wdp_b4</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (B1)</t>
+          <t>Water Depletion Potential (B4)</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -19805,12 +19805,12 @@
     <row r="313">
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>pert_b2</t>
+          <t>wdp_b5</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (B2)</t>
+          <t>Water Depletion Potential (B5)</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
@@ -19829,12 +19829,12 @@
     <row r="314">
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>pert_b3</t>
+          <t>wdp_b6</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (B3)</t>
+          <t>Water Depletion Potential (B6)</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
@@ -19853,12 +19853,12 @@
     <row r="315">
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>pert_b4</t>
+          <t>wdp_c1</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (B4)</t>
+          <t>Water Depletion Potential (C1)</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
@@ -19877,12 +19877,12 @@
     <row r="316">
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>pert_b5</t>
+          <t>wdp_c2</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (B5)</t>
+          <t>Water Depletion Potential (C2)</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
@@ -19901,12 +19901,12 @@
     <row r="317">
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>pert_b6</t>
+          <t>wdp_c3</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (B6)</t>
+          <t>Water Depletion Potential (C3)</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
@@ -19925,12 +19925,12 @@
     <row r="318">
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>pert_c1</t>
+          <t>wdp_c4</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (C1)</t>
+          <t>Water Depletion Potential (C4)</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
@@ -19949,12 +19949,12 @@
     <row r="319">
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>pert_c2</t>
+          <t>wdp_d</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (C2)</t>
+          <t>Water Depletion Potential (D)</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
@@ -19973,12 +19973,12 @@
     <row r="320">
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>pert_c3</t>
+          <t>wdp_d1</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (C3)</t>
+          <t>Water Depletion Potential (D1)</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
@@ -19997,12 +19997,12 @@
     <row r="321">
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>pert_c4</t>
+          <t>wdp_d2</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (C4)</t>
+          <t>Water Depletion Potential (D2)</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
@@ -20021,12 +20021,12 @@
     <row r="322">
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>pert_d</t>
+          <t>wdp_total</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (D)</t>
+          <t>Total Water Depletion Potential</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -20045,12 +20045,12 @@
     <row r="323">
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>pert_d1</t>
+          <t>pere_a1_a3</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (D1)</t>
+          <t>Primary Energy Renewable (Energy resources) (A1-A3)</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
@@ -20069,12 +20069,12 @@
     <row r="324">
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>pert_d2</t>
+          <t>pere_a1</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Renewable Total (D2)</t>
+          <t>Primary Energy Renewable (Energy resources) (A1)</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
@@ -20093,12 +20093,12 @@
     <row r="325">
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>pert_total</t>
+          <t>pere_a2</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
         <is>
-          <t>Total Primary Energy Renewable Total</t>
+          <t>Primary Energy Renewable (Energy resources) (A2)</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -20117,12 +20117,12 @@
     <row r="326">
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>penrt_a1_a3</t>
+          <t>pere_a3</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (A1-A3)</t>
+          <t>Primary Energy Renewable (Energy resources) (A3)</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
@@ -20141,12 +20141,12 @@
     <row r="327">
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>penrt_a4</t>
+          <t>pere_a4</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (A4)</t>
+          <t>Primary Energy Renewable (Energy resources) (A4)</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
@@ -20165,12 +20165,12 @@
     <row r="328">
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>penrt_a5</t>
+          <t>pere_a5</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (A5)</t>
+          <t>Primary Energy Renewable (Energy resources) (A5)</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
@@ -20189,12 +20189,12 @@
     <row r="329">
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>penrt_b1</t>
+          <t>pere_b1</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (B1)</t>
+          <t>Primary Energy Renewable (Energy resources) (B1)</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
@@ -20213,12 +20213,12 @@
     <row r="330">
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>penrt_b2</t>
+          <t>pere_b2</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (B2)</t>
+          <t>Primary Energy Renewable (Energy resources) (B2)</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
@@ -20237,12 +20237,12 @@
     <row r="331">
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>penrt_b3</t>
+          <t>pere_b3</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (B3)</t>
+          <t>Primary Energy Renewable (Energy resources) (B3)</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
@@ -20261,12 +20261,12 @@
     <row r="332">
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>penrt_b4</t>
+          <t>pere_b4</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (B4)</t>
+          <t>Primary Energy Renewable (Energy resources) (B4)</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
@@ -20285,12 +20285,12 @@
     <row r="333">
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>penrt_b5</t>
+          <t>pere_b5</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (B5)</t>
+          <t>Primary Energy Renewable (Energy resources) (B5)</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
@@ -20309,12 +20309,12 @@
     <row r="334">
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>penrt_b6</t>
+          <t>pere_b6</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (B6)</t>
+          <t>Primary Energy Renewable (Energy resources) (B6)</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
@@ -20333,12 +20333,12 @@
     <row r="335">
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>penrt_c1</t>
+          <t>pere_c1</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (C1)</t>
+          <t>Primary Energy Renewable (Energy resources) (C1)</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
@@ -20357,12 +20357,12 @@
     <row r="336">
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>penrt_c2</t>
+          <t>pere_c2</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (C2)</t>
+          <t>Primary Energy Renewable (Energy resources) (C2)</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
@@ -20381,12 +20381,12 @@
     <row r="337">
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>penrt_c3</t>
+          <t>pere_c3</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (C3)</t>
+          <t>Primary Energy Renewable (Energy resources) (C3)</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
@@ -20405,12 +20405,12 @@
     <row r="338">
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>penrt_c4</t>
+          <t>pere_c4</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (C4)</t>
+          <t>Primary Energy Renewable (Energy resources) (C4)</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
@@ -20429,12 +20429,12 @@
     <row r="339">
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>penrt_d</t>
+          <t>pere_d</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (D)</t>
+          <t>Primary Energy Renewable (Energy resources) (D)</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
@@ -20453,12 +20453,12 @@
     <row r="340">
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>penrt_d1</t>
+          <t>pere_d1</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (D1)</t>
+          <t>Primary Energy Renewable (Energy resources) (D1)</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
@@ -20477,12 +20477,12 @@
     <row r="341">
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>penrt_d2</t>
+          <t>pere_d2</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
         <is>
-          <t>Primary Energy Non-Renewable Total (D2)</t>
+          <t>Primary Energy Renewable (Energy resources) (D2)</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
@@ -20501,12 +20501,12 @@
     <row r="342">
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>penrt_total</t>
+          <t>pere_total</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t>Total Primary Energy Non-Renewable Total</t>
+          <t>Total Primary Energy Renewable (Energy resources)</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
@@ -20521,6 +20521,1446 @@
       </c>
       <c r="F342" s="5" t="inlineStr"/>
       <c r="G342" s="5" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>penre_a1_a3</t>
+        </is>
+      </c>
+      <c r="C343" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (A1-A3)</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E343" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F343" s="5" t="inlineStr"/>
+      <c r="G343" s="5" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>penre_a1</t>
+        </is>
+      </c>
+      <c r="C344" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (A1)</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E344" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F344" s="5" t="inlineStr"/>
+      <c r="G344" s="5" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>penre_a2</t>
+        </is>
+      </c>
+      <c r="C345" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (A2)</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E345" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F345" s="5" t="inlineStr"/>
+      <c r="G345" s="5" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>penre_a3</t>
+        </is>
+      </c>
+      <c r="C346" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (A3)</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E346" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F346" s="5" t="inlineStr"/>
+      <c r="G346" s="5" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>penre_a4</t>
+        </is>
+      </c>
+      <c r="C347" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (A4)</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E347" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F347" s="5" t="inlineStr"/>
+      <c r="G347" s="5" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>penre_a5</t>
+        </is>
+      </c>
+      <c r="C348" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (A5)</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E348" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F348" s="5" t="inlineStr"/>
+      <c r="G348" s="5" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>penre_b1</t>
+        </is>
+      </c>
+      <c r="C349" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (B1)</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E349" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F349" s="5" t="inlineStr"/>
+      <c r="G349" s="5" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>penre_b2</t>
+        </is>
+      </c>
+      <c r="C350" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (B2)</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E350" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F350" s="5" t="inlineStr"/>
+      <c r="G350" s="5" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>penre_b3</t>
+        </is>
+      </c>
+      <c r="C351" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (B3)</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E351" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F351" s="5" t="inlineStr"/>
+      <c r="G351" s="5" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>penre_b4</t>
+        </is>
+      </c>
+      <c r="C352" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (B4)</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E352" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F352" s="5" t="inlineStr"/>
+      <c r="G352" s="5" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>penre_b5</t>
+        </is>
+      </c>
+      <c r="C353" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (B5)</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E353" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F353" s="5" t="inlineStr"/>
+      <c r="G353" s="5" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>penre_b6</t>
+        </is>
+      </c>
+      <c r="C354" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (B6)</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E354" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F354" s="5" t="inlineStr"/>
+      <c r="G354" s="5" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>penre_c1</t>
+        </is>
+      </c>
+      <c r="C355" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (C1)</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E355" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F355" s="5" t="inlineStr"/>
+      <c r="G355" s="5" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>penre_c2</t>
+        </is>
+      </c>
+      <c r="C356" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (C2)</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E356" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F356" s="5" t="inlineStr"/>
+      <c r="G356" s="5" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>penre_c3</t>
+        </is>
+      </c>
+      <c r="C357" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (C3)</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E357" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F357" s="5" t="inlineStr"/>
+      <c r="G357" s="5" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>penre_c4</t>
+        </is>
+      </c>
+      <c r="C358" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (C4)</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E358" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F358" s="5" t="inlineStr"/>
+      <c r="G358" s="5" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>penre_d</t>
+        </is>
+      </c>
+      <c r="C359" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (D)</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E359" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F359" s="5" t="inlineStr"/>
+      <c r="G359" s="5" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>penre_d1</t>
+        </is>
+      </c>
+      <c r="C360" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (D1)</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E360" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F360" s="5" t="inlineStr"/>
+      <c r="G360" s="5" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>penre_d2</t>
+        </is>
+      </c>
+      <c r="C361" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable (Energy resources) (D2)</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E361" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F361" s="5" t="inlineStr"/>
+      <c r="G361" s="5" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>penre_total</t>
+        </is>
+      </c>
+      <c r="C362" s="1" t="inlineStr">
+        <is>
+          <t>Total Primary Energy Non-Renewable (Energy resources)</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E362" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F362" s="5" t="inlineStr"/>
+      <c r="G362" s="5" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>pert_a1_a3</t>
+        </is>
+      </c>
+      <c r="C363" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (A1-A3)</t>
+        </is>
+      </c>
+      <c r="D363" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E363" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F363" s="5" t="inlineStr"/>
+      <c r="G363" s="5" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>pert_a1</t>
+        </is>
+      </c>
+      <c r="C364" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (A1)</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E364" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F364" s="5" t="inlineStr"/>
+      <c r="G364" s="5" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>pert_a2</t>
+        </is>
+      </c>
+      <c r="C365" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (A2)</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E365" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F365" s="5" t="inlineStr"/>
+      <c r="G365" s="5" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>pert_a3</t>
+        </is>
+      </c>
+      <c r="C366" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (A3)</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E366" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F366" s="5" t="inlineStr"/>
+      <c r="G366" s="5" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>pert_a4</t>
+        </is>
+      </c>
+      <c r="C367" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (A4)</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E367" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F367" s="5" t="inlineStr"/>
+      <c r="G367" s="5" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>pert_a5</t>
+        </is>
+      </c>
+      <c r="C368" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (A5)</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E368" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F368" s="5" t="inlineStr"/>
+      <c r="G368" s="5" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>pert_b1</t>
+        </is>
+      </c>
+      <c r="C369" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (B1)</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E369" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F369" s="5" t="inlineStr"/>
+      <c r="G369" s="5" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>pert_b2</t>
+        </is>
+      </c>
+      <c r="C370" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (B2)</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E370" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F370" s="5" t="inlineStr"/>
+      <c r="G370" s="5" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>pert_b3</t>
+        </is>
+      </c>
+      <c r="C371" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (B3)</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E371" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F371" s="5" t="inlineStr"/>
+      <c r="G371" s="5" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>pert_b4</t>
+        </is>
+      </c>
+      <c r="C372" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (B4)</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E372" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F372" s="5" t="inlineStr"/>
+      <c r="G372" s="5" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>pert_b5</t>
+        </is>
+      </c>
+      <c r="C373" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (B5)</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E373" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F373" s="5" t="inlineStr"/>
+      <c r="G373" s="5" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>pert_b6</t>
+        </is>
+      </c>
+      <c r="C374" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (B6)</t>
+        </is>
+      </c>
+      <c r="D374" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E374" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F374" s="5" t="inlineStr"/>
+      <c r="G374" s="5" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>pert_c1</t>
+        </is>
+      </c>
+      <c r="C375" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (C1)</t>
+        </is>
+      </c>
+      <c r="D375" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E375" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F375" s="5" t="inlineStr"/>
+      <c r="G375" s="5" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>pert_c2</t>
+        </is>
+      </c>
+      <c r="C376" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (C2)</t>
+        </is>
+      </c>
+      <c r="D376" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E376" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F376" s="5" t="inlineStr"/>
+      <c r="G376" s="5" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>pert_c3</t>
+        </is>
+      </c>
+      <c r="C377" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (C3)</t>
+        </is>
+      </c>
+      <c r="D377" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E377" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F377" s="5" t="inlineStr"/>
+      <c r="G377" s="5" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>pert_c4</t>
+        </is>
+      </c>
+      <c r="C378" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (C4)</t>
+        </is>
+      </c>
+      <c r="D378" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E378" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F378" s="5" t="inlineStr"/>
+      <c r="G378" s="5" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>pert_d</t>
+        </is>
+      </c>
+      <c r="C379" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (D)</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E379" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F379" s="5" t="inlineStr"/>
+      <c r="G379" s="5" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>pert_d1</t>
+        </is>
+      </c>
+      <c r="C380" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (D1)</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E380" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F380" s="5" t="inlineStr"/>
+      <c r="G380" s="5" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>pert_d2</t>
+        </is>
+      </c>
+      <c r="C381" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Renewable Total (D2)</t>
+        </is>
+      </c>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E381" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F381" s="5" t="inlineStr"/>
+      <c r="G381" s="5" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>pert_total</t>
+        </is>
+      </c>
+      <c r="C382" s="1" t="inlineStr">
+        <is>
+          <t>Total Primary Energy Renewable Total</t>
+        </is>
+      </c>
+      <c r="D382" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E382" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F382" s="5" t="inlineStr"/>
+      <c r="G382" s="5" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>penrt_a1_a3</t>
+        </is>
+      </c>
+      <c r="C383" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (A1-A3)</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E383" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F383" s="5" t="inlineStr"/>
+      <c r="G383" s="5" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>penrt_a1</t>
+        </is>
+      </c>
+      <c r="C384" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (A1)</t>
+        </is>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E384" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F384" s="5" t="inlineStr"/>
+      <c r="G384" s="5" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>penrt_a2</t>
+        </is>
+      </c>
+      <c r="C385" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (A2)</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E385" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F385" s="5" t="inlineStr"/>
+      <c r="G385" s="5" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>penrt_a3</t>
+        </is>
+      </c>
+      <c r="C386" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (A3)</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E386" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F386" s="5" t="inlineStr"/>
+      <c r="G386" s="5" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>penrt_a4</t>
+        </is>
+      </c>
+      <c r="C387" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (A4)</t>
+        </is>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E387" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F387" s="5" t="inlineStr"/>
+      <c r="G387" s="5" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>penrt_a5</t>
+        </is>
+      </c>
+      <c r="C388" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (A5)</t>
+        </is>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E388" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F388" s="5" t="inlineStr"/>
+      <c r="G388" s="5" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>penrt_b1</t>
+        </is>
+      </c>
+      <c r="C389" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (B1)</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E389" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F389" s="5" t="inlineStr"/>
+      <c r="G389" s="5" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>penrt_b2</t>
+        </is>
+      </c>
+      <c r="C390" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (B2)</t>
+        </is>
+      </c>
+      <c r="D390" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E390" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F390" s="5" t="inlineStr"/>
+      <c r="G390" s="5" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>penrt_b3</t>
+        </is>
+      </c>
+      <c r="C391" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (B3)</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E391" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F391" s="5" t="inlineStr"/>
+      <c r="G391" s="5" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>penrt_b4</t>
+        </is>
+      </c>
+      <c r="C392" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (B4)</t>
+        </is>
+      </c>
+      <c r="D392" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E392" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F392" s="5" t="inlineStr"/>
+      <c r="G392" s="5" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>penrt_b5</t>
+        </is>
+      </c>
+      <c r="C393" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (B5)</t>
+        </is>
+      </c>
+      <c r="D393" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E393" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F393" s="5" t="inlineStr"/>
+      <c r="G393" s="5" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>penrt_b6</t>
+        </is>
+      </c>
+      <c r="C394" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (B6)</t>
+        </is>
+      </c>
+      <c r="D394" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E394" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F394" s="5" t="inlineStr"/>
+      <c r="G394" s="5" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>penrt_c1</t>
+        </is>
+      </c>
+      <c r="C395" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (C1)</t>
+        </is>
+      </c>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E395" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F395" s="5" t="inlineStr"/>
+      <c r="G395" s="5" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>penrt_c2</t>
+        </is>
+      </c>
+      <c r="C396" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (C2)</t>
+        </is>
+      </c>
+      <c r="D396" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E396" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F396" s="5" t="inlineStr"/>
+      <c r="G396" s="5" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>penrt_c3</t>
+        </is>
+      </c>
+      <c r="C397" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (C3)</t>
+        </is>
+      </c>
+      <c r="D397" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E397" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F397" s="5" t="inlineStr"/>
+      <c r="G397" s="5" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>penrt_c4</t>
+        </is>
+      </c>
+      <c r="C398" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (C4)</t>
+        </is>
+      </c>
+      <c r="D398" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E398" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F398" s="5" t="inlineStr"/>
+      <c r="G398" s="5" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>penrt_d</t>
+        </is>
+      </c>
+      <c r="C399" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (D)</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E399" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F399" s="5" t="inlineStr"/>
+      <c r="G399" s="5" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>penrt_d1</t>
+        </is>
+      </c>
+      <c r="C400" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (D1)</t>
+        </is>
+      </c>
+      <c r="D400" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E400" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F400" s="5" t="inlineStr"/>
+      <c r="G400" s="5" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>penrt_d2</t>
+        </is>
+      </c>
+      <c r="C401" s="1" t="inlineStr">
+        <is>
+          <t>Primary Energy Non-Renewable Total (D2)</t>
+        </is>
+      </c>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E401" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F401" s="5" t="inlineStr"/>
+      <c r="G401" s="5" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>penrt_total</t>
+        </is>
+      </c>
+      <c r="C402" s="1" t="inlineStr">
+        <is>
+          <t>Total Primary Energy Non-Renewable Total</t>
+        </is>
+      </c>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="E402" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="F402" s="5" t="inlineStr"/>
+      <c r="G402" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
